--- a/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
+++ b/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="AH8" s="71" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">

--- a/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
+++ b/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="119">
   <si>
     <r>
       <t xml:space="preserve">Đơn vị: </t>
@@ -75,6 +75,130 @@
     <t>Quy ra công</t>
   </si>
   <si>
+    <t xml:space="preserve">1
+T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2
+T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3
+T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4
+T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5
+CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6
+T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7
+T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8
+T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9
+T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10
+T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11
+T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12
+CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13
+T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14
+T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15
+T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16
+T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17
+T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18
+T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19
+CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20
+T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21
+T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22
+T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23
+T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24
+T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25
+T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26
+CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27
+T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28
+T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29
+T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30
+T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31
+T6</t>
+  </si>
+  <si>
     <t>Số công hưởng lương thời gian</t>
   </si>
   <si>
@@ -144,7 +268,7 @@
     <t>Phụ trách bộ phận</t>
   </si>
   <si>
-    <t>Thủ trưởng đơn vị</t>
+    <t>Trưởng khoa</t>
   </si>
   <si>
     <t>Bác sĩ Nguyễn Văn Trưởng</t>
@@ -307,7 +431,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -361,8 +485,12 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <family val="1"/>
-      <sz val="9"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -463,7 +591,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -479,12 +607,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.3499862666707358"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,7 +730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -641,7 +763,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -662,13 +784,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -683,16 +805,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -703,147 +822,129 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -853,10 +954,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -883,18 +984,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2325,116 +2426,116 @@
     <row r="7" ht="63" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="16">
-        <v>1</v>
-      </c>
-      <c r="D7" s="16">
-        <v>2</v>
-      </c>
-      <c r="E7" s="16">
-        <v>3</v>
-      </c>
-      <c r="F7" s="17">
-        <v>4</v>
-      </c>
-      <c r="G7" s="17">
-        <v>5</v>
-      </c>
-      <c r="H7" s="16">
-        <v>6</v>
-      </c>
-      <c r="I7" s="16">
-        <v>7</v>
-      </c>
-      <c r="J7" s="16">
-        <v>8</v>
-      </c>
-      <c r="K7" s="16">
-        <v>9</v>
-      </c>
-      <c r="L7" s="16">
-        <v>10</v>
-      </c>
-      <c r="M7" s="17">
-        <v>11</v>
-      </c>
-      <c r="N7" s="17">
+      <c r="C7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="16">
+      <c r="D7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="16">
+      <c r="E7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="F7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="16">
+      <c r="G7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="16">
+      <c r="H7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="17">
+      <c r="I7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="U7" s="17">
+      <c r="J7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="V7" s="16">
+      <c r="K7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="W7" s="16">
+      <c r="L7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="X7" s="16">
+      <c r="M7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Y7" s="16">
+      <c r="N7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="Z7" s="16">
+      <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AA7" s="17">
+      <c r="P7" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="AB7" s="17">
+      <c r="Q7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AC7" s="16">
+      <c r="R7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AD7" s="16">
+      <c r="S7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AE7" s="16">
+      <c r="T7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="AF7" s="16">
+      <c r="U7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="AG7" s="16">
+      <c r="V7" s="16" t="s">
         <v>31</v>
       </c>
+      <c r="W7" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="X7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB7" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE7" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG7" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="AH7" s="18" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="AI7" s="18" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="AJ7" s="19" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="AK7" s="19" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="AL7" s="20" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="AM7" s="20" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -2442,100 +2543,100 @@
         <v>1</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="U8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Z8" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AA8" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AE8" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AF8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AG8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AH8" s="25">
         <v>23</v>
@@ -2555,100 +2656,100 @@
         <v>2</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N9" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="W9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z9" s="23" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AA9" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AB9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AE9" s="23" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="AF9" s="23" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="AG9" s="23" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="AH9" s="25">
         <v>23</v>
@@ -2664,100 +2765,100 @@
         <v>3</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="W10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="X10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z10" s="23" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AA10" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AB10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AD10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AE10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AF10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AG10" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AH10" s="25">
         <v>23</v>
@@ -2773,100 +2874,100 @@
         <v>4</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M11" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="W11" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Z11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AA11" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB11" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AC11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AE11" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AF11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AG11" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AH11" s="25">
         <v>23</v>
@@ -2886,100 +2987,100 @@
         <v>5</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="R12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U12" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="W12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="X12" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Y12" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Z12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AA12" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AB12" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AE12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AF12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AG12" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AH12" s="25">
         <v>23</v>
@@ -2999,100 +3100,100 @@
         <v>6</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="M13" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N13" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="O13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="P13" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="R13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="U13" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V13" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="W13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="Y13" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AA13" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AB13" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AD13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AE13" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AF13" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AG13" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AH13" s="25">
         <v>23</v>
@@ -3112,100 +3213,100 @@
         <v>7</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="R14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S14" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U14" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V14" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="W14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y14" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Z14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AA14" s="24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AB14" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AC14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AD14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AE14" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AF14" s="23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AG14" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AH14" s="25">
         <v>23</v>
@@ -3223,39 +3324,39 @@
     <row r="15" ht="22.5" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
       <c r="B15" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
-      <c r="AC15" s="30"/>
-      <c r="AD15" s="30"/>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
+        <v>62</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="28"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
       <c r="AH15" s="26">
         <f>SUM(AH8:AH14)</f>
       </c>
@@ -3302,27 +3403,27 @@
       <c r="X16" s="8"/>
       <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
-      <c r="AA16" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB16" s="31"/>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
-      <c r="AF16" s="31"/>
-      <c r="AG16" s="31"/>
-      <c r="AH16" s="31"/>
-      <c r="AI16" s="31"/>
-      <c r="AJ16" s="31"/>
-      <c r="AK16" s="31"/>
-      <c r="AL16" s="31"/>
-      <c r="AM16" s="31"/>
+      <c r="AA16" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB16" s="30"/>
+      <c r="AC16" s="30"/>
+      <c r="AD16" s="30"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="30"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="30"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="30"/>
+      <c r="AM16" s="30"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="32"/>
+      <c r="A17" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="31"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -3332,134 +3433,65 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
+      <c r="L17" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AA17" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="32"/>
-      <c r="AE17" s="32"/>
-      <c r="AF17" s="32"/>
-      <c r="AG17" s="32"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="32"/>
-      <c r="AJ17" s="32"/>
-      <c r="AK17" s="32"/>
-      <c r="AL17" s="32"/>
-      <c r="AM17" s="32"/>
+      <c r="AA17" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB17" s="31"/>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="31"/>
+      <c r="AE17" s="31"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="31"/>
+      <c r="AH17" s="31"/>
+      <c r="AI17" s="31"/>
+      <c r="AJ17" s="31"/>
+      <c r="AK17" s="31"/>
+      <c r="AL17" s="31"/>
+      <c r="AM17" s="31"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="P21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="R21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V21" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM21" s="33" t="s">
-        <v>36</v>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA21" s="32" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="C22" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -3475,374 +3507,374 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="32"/>
-      <c r="AG22" s="32"/>
-      <c r="AH22" s="32"/>
-      <c r="AI22" s="32"/>
-      <c r="AJ22" s="32"/>
-      <c r="AK22" s="32"/>
-      <c r="AL22" s="35"/>
-      <c r="AM22" s="32"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="31"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="31"/>
+      <c r="AK22" s="31"/>
+      <c r="AL22" s="34"/>
+      <c r="AM22" s="31"/>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="L23" s="39"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="40"/>
-      <c r="U23" s="40"/>
-      <c r="V23" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="W23" s="40"/>
-      <c r="X23" s="40"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="40"/>
-      <c r="AA23" s="40"/>
-      <c r="AB23" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC23" s="39"/>
-      <c r="AD23" s="40"/>
-      <c r="AE23" s="40"/>
-      <c r="AF23" s="40"/>
-      <c r="AG23" s="40"/>
-      <c r="AH23" s="41"/>
-      <c r="AI23" s="41"/>
-      <c r="AJ23" s="41"/>
-      <c r="AK23" s="41"/>
-      <c r="AL23" s="41"/>
-      <c r="AM23" s="40"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="38"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="39"/>
+      <c r="V23" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="W23" s="39"/>
+      <c r="X23" s="39"/>
+      <c r="Y23" s="39"/>
+      <c r="Z23" s="39"/>
+      <c r="AA23" s="39"/>
+      <c r="AB23" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC23" s="38"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="39"/>
+      <c r="AF23" s="39"/>
+      <c r="AG23" s="39"/>
+      <c r="AH23" s="40"/>
+      <c r="AI23" s="40"/>
+      <c r="AJ23" s="40"/>
+      <c r="AK23" s="40"/>
+      <c r="AL23" s="40"/>
+      <c r="AM23" s="39"/>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A24" s="42"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="L24" s="39"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="40"/>
-      <c r="V24" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="W24" s="40"/>
-      <c r="X24" s="40"/>
-      <c r="Y24" s="40"/>
-      <c r="Z24" s="40"/>
-      <c r="AA24" s="40"/>
-      <c r="AB24" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC24" s="40"/>
-      <c r="AD24" s="40"/>
-      <c r="AE24" s="40"/>
-      <c r="AF24" s="40"/>
-      <c r="AG24" s="40"/>
-      <c r="AH24" s="42"/>
-      <c r="AI24" s="42"/>
-      <c r="AJ24" s="42"/>
-      <c r="AK24" s="42"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="L24" s="38"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="39"/>
+      <c r="V24" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="W24" s="39"/>
+      <c r="X24" s="39"/>
+      <c r="Y24" s="39"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="39"/>
+      <c r="AB24" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="39"/>
+      <c r="AE24" s="39"/>
+      <c r="AF24" s="39"/>
+      <c r="AG24" s="39"/>
+      <c r="AH24" s="41"/>
+      <c r="AI24" s="41"/>
+      <c r="AJ24" s="41"/>
+      <c r="AK24" s="41"/>
       <c r="AL24" s="6"/>
-      <c r="AM24" s="42"/>
+      <c r="AM24" s="41"/>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A25" s="42"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="L25" s="39"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="40"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="40"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="40"/>
-      <c r="U25" s="40"/>
-      <c r="V25" s="40" t="s">
+      <c r="A25" s="41"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="L25" s="38"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="39"/>
+      <c r="S25" s="39"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="39"/>
+      <c r="V25" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="W25" s="39"/>
+      <c r="X25" s="39"/>
+      <c r="Y25" s="39"/>
+      <c r="Z25" s="39"/>
+      <c r="AA25" s="39"/>
+      <c r="AB25" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC25" s="38"/>
+      <c r="AD25" s="39"/>
+      <c r="AE25" s="39"/>
+      <c r="AF25" s="39"/>
+      <c r="AG25" s="39"/>
+      <c r="AH25" s="41"/>
+      <c r="AI25" s="41"/>
+      <c r="AJ25" s="41"/>
+      <c r="AK25" s="41"/>
+      <c r="AL25" s="6"/>
+      <c r="AM25" s="41"/>
+    </row>
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A26" s="41"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" s="38"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="W25" s="40"/>
-      <c r="X25" s="40"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="40"/>
-      <c r="AA25" s="40"/>
-      <c r="AB25" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC25" s="39"/>
-      <c r="AD25" s="40"/>
-      <c r="AE25" s="40"/>
-      <c r="AF25" s="40"/>
-      <c r="AG25" s="40"/>
-      <c r="AH25" s="42"/>
-      <c r="AI25" s="42"/>
-      <c r="AJ25" s="42"/>
-      <c r="AK25" s="42"/>
-      <c r="AL25" s="6"/>
-      <c r="AM25" s="42"/>
-    </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A26" s="42"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="L26" s="39"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="40"/>
-      <c r="U26" s="40"/>
-      <c r="V26" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC26" s="39"/>
-      <c r="AD26" s="40"/>
-      <c r="AE26" s="40"/>
-      <c r="AF26" s="40"/>
-      <c r="AG26" s="40"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="42"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AB26" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="39"/>
+      <c r="AE26" s="39"/>
+      <c r="AF26" s="39"/>
+      <c r="AG26" s="39"/>
+      <c r="AH26" s="41"/>
+      <c r="AI26" s="41"/>
+      <c r="AJ26" s="41"/>
+      <c r="AK26" s="41"/>
       <c r="AL26" s="6"/>
-      <c r="AM26" s="42"/>
+      <c r="AM26" s="41"/>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A27" s="42"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="L27" s="39"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="40"/>
-      <c r="U27" s="40"/>
-      <c r="V27" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="W27" s="40"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="40"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC27" s="39"/>
-      <c r="AD27" s="40"/>
-      <c r="AE27" s="40"/>
-      <c r="AF27" s="40"/>
-      <c r="AG27" s="40"/>
-      <c r="AH27" s="42"/>
-      <c r="AI27" s="42"/>
-      <c r="AJ27" s="42"/>
-      <c r="AK27" s="42"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="L27" s="38"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="39"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="39"/>
+      <c r="V27" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="W27" s="39"/>
+      <c r="X27" s="39"/>
+      <c r="Y27" s="39"/>
+      <c r="Z27" s="39"/>
+      <c r="AA27" s="39"/>
+      <c r="AB27" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC27" s="38"/>
+      <c r="AD27" s="39"/>
+      <c r="AE27" s="39"/>
+      <c r="AF27" s="39"/>
+      <c r="AG27" s="39"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="41"/>
+      <c r="AJ27" s="41"/>
+      <c r="AK27" s="41"/>
       <c r="AL27" s="6"/>
-      <c r="AM27" s="36"/>
+      <c r="AM27" s="35"/>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="39" t="s">
+      <c r="A28" s="44"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="39"/>
+      <c r="Z28" s="39"/>
+      <c r="AA28" s="39"/>
+      <c r="AB28" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC28" s="38"/>
+      <c r="AD28" s="39"/>
+      <c r="AE28" s="39"/>
+      <c r="AF28" s="39"/>
+      <c r="AG28" s="39"/>
+      <c r="AH28" s="44"/>
+      <c r="AI28" s="44"/>
+      <c r="AJ28" s="44"/>
+      <c r="AK28" s="44"/>
+      <c r="AL28" s="44"/>
+      <c r="AM28" s="44"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A29" s="41"/>
+      <c r="C29" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="39"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="41"/>
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="41"/>
+      <c r="AL29" s="45"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="C30" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="K30" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="V30" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="W30" s="39"/>
+      <c r="X30" s="39"/>
+      <c r="Y30" s="39"/>
+      <c r="Z30" s="39"/>
+      <c r="AA30" s="39"/>
+      <c r="AB30" s="39" t="s">
         <v>54</v>
-      </c>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="39"/>
-      <c r="U28" s="39"/>
-      <c r="V28" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="W28" s="40"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="40"/>
-      <c r="Z28" s="40"/>
-      <c r="AA28" s="40"/>
-      <c r="AB28" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC28" s="39"/>
-      <c r="AD28" s="40"/>
-      <c r="AE28" s="40"/>
-      <c r="AF28" s="40"/>
-      <c r="AG28" s="40"/>
-      <c r="AH28" s="45"/>
-      <c r="AI28" s="45"/>
-      <c r="AJ28" s="45"/>
-      <c r="AK28" s="45"/>
-      <c r="AL28" s="45"/>
-      <c r="AM28" s="45"/>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A29" s="42"/>
-      <c r="C29" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="40"/>
-      <c r="U29" s="40"/>
-      <c r="V29" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="W29" s="40"/>
-      <c r="X29" s="40"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="40"/>
-      <c r="AA29" s="40"/>
-      <c r="AB29" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC29" s="40"/>
-      <c r="AD29" s="42"/>
-      <c r="AE29" s="42"/>
-      <c r="AF29" s="42"/>
-      <c r="AG29" s="42"/>
-      <c r="AL29" s="46"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C30" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="K30" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="V30" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="W30" s="40"/>
-      <c r="X30" s="40"/>
-      <c r="Y30" s="40"/>
-      <c r="Z30" s="40"/>
-      <c r="AA30" s="40"/>
-      <c r="AB30" s="40" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3885,184 +3917,184 @@
   <dimension ref="A1:AK24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
-    <col min="1" max="1" width="4" style="47" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" style="47" customWidth="1"/>
-    <col min="3" max="33" width="3.140625" style="47" customWidth="1"/>
-    <col min="34" max="34" width="7" style="48" customWidth="1"/>
-    <col min="35" max="36" width="6" style="48" customWidth="1"/>
-    <col min="37" max="37" width="6.140625" style="48" customWidth="1"/>
-    <col min="38" max="38" width="12.140625" style="47" customWidth="1"/>
-    <col min="39" max="39" width="0.28515625" style="47" customWidth="1"/>
-    <col min="40" max="40" width="9.140625" style="47" customWidth="1"/>
-    <col min="41" max="41" width="7.140625" style="47" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="47" customWidth="1"/>
+    <col min="1" max="1" width="4" style="46" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" style="46" customWidth="1"/>
+    <col min="3" max="33" width="3.140625" style="46" customWidth="1"/>
+    <col min="34" max="34" width="7" style="47" customWidth="1"/>
+    <col min="35" max="36" width="6" style="47" customWidth="1"/>
+    <col min="37" max="37" width="6.140625" style="47" customWidth="1"/>
+    <col min="38" max="38" width="12.140625" style="46" customWidth="1"/>
+    <col min="39" max="39" width="0.28515625" style="46" customWidth="1"/>
+    <col min="40" max="40" width="9.140625" style="46" customWidth="1"/>
+    <col min="41" max="41" width="7.140625" style="46" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
-      <c r="AB1" s="50"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="50"/>
-      <c r="AE1" s="50"/>
-      <c r="AF1" s="50"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
+      <c r="A1" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="52"/>
-      <c r="AA2" s="52"/>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
-    </row>
-    <row r="3" ht="19.5" customHeight="1" spans="1:37" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-    </row>
-    <row r="4" ht="19.5" customHeight="1" spans="1:37" s="53" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="53"/>
-      <c r="T4" s="53"/>
-      <c r="U4" s="53"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="53"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="53"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="53"/>
-      <c r="AB4" s="53"/>
-      <c r="AC4" s="53"/>
-      <c r="AD4" s="53"/>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="53"/>
-      <c r="AH4" s="55"/>
-      <c r="AI4" s="55"/>
-      <c r="AJ4" s="55"/>
-      <c r="AK4" s="55"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1" spans="1:37" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="52"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="52"/>
+      <c r="AF3" s="52"/>
+      <c r="AG3" s="52"/>
+      <c r="AH3" s="54"/>
+      <c r="AI3" s="54"/>
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1" spans="1:37" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="52"/>
+      <c r="AF4" s="52"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="54"/>
+      <c r="AI4" s="54"/>
+      <c r="AJ4" s="54"/>
+      <c r="AK4" s="54"/>
     </row>
     <row r="5" ht="23.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
@@ -4105,7 +4137,7 @@
       <c r="AF5" s="14"/>
       <c r="AG5" s="15"/>
       <c r="AH5" s="13" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="AI5" s="14"/>
       <c r="AJ5" s="14"/>
@@ -4114,110 +4146,110 @@
     <row r="6" ht="42" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="12"/>
-      <c r="C6" s="16">
-        <v>1</v>
-      </c>
-      <c r="D6" s="16">
-        <v>2</v>
-      </c>
-      <c r="E6" s="16">
-        <v>3</v>
-      </c>
-      <c r="F6" s="17">
-        <v>4</v>
-      </c>
-      <c r="G6" s="17">
-        <v>5</v>
-      </c>
-      <c r="H6" s="16">
-        <v>6</v>
-      </c>
-      <c r="I6" s="16">
-        <v>7</v>
-      </c>
-      <c r="J6" s="16">
-        <v>8</v>
-      </c>
-      <c r="K6" s="16">
-        <v>9</v>
-      </c>
-      <c r="L6" s="16">
-        <v>10</v>
-      </c>
-      <c r="M6" s="17">
-        <v>11</v>
-      </c>
-      <c r="N6" s="17">
+      <c r="C6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="16">
+      <c r="D6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="P6" s="16">
+      <c r="E6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="F6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="R6" s="16">
+      <c r="G6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S6" s="16">
+      <c r="H6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="T6" s="17">
+      <c r="I6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="U6" s="17">
+      <c r="J6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="V6" s="16">
+      <c r="K6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="W6" s="16">
+      <c r="L6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="X6" s="16">
+      <c r="M6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Y6" s="16">
+      <c r="N6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="Z6" s="16">
+      <c r="O6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AA6" s="17">
+      <c r="P6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="AB6" s="17">
+      <c r="Q6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AC6" s="16">
+      <c r="R6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AD6" s="16">
+      <c r="S6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AE6" s="16">
+      <c r="T6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="AF6" s="16">
+      <c r="U6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="AG6" s="16">
+      <c r="V6" s="16" t="s">
         <v>31</v>
       </c>
+      <c r="W6" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="X6" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z6" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB6" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD6" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG6" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="AH6" s="18" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="AI6" s="18" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="AJ6" s="19" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AK6" s="19" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -4225,100 +4257,100 @@
         <v>1</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="N7" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="P7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="U7" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="W7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Y7" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Z7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA7" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AB7" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AD7" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AE7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AF7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AG7" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AH7" s="25">
         <v>4</v>
@@ -4336,100 +4368,100 @@
         <v>2</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Y8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Z8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA8" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AE8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AF8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AG8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AH8" s="25">
         <v>9</v>
@@ -4447,100 +4479,100 @@
         <v>3</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="N9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="W9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Y9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Z9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AB9" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AE9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AF9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AG9" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AH9" s="25">
         <v>1</v>
@@ -4556,100 +4588,100 @@
         <v>4</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="U10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="W10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="X10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Y10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Z10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AA10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AB10" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AD10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AE10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AF10" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AG10" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AH10" s="25">
         <v>8</v>
@@ -4667,100 +4699,100 @@
         <v>5</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="M11" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="W11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Y11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Z11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA11" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AB11" s="24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AC11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AE11" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AF11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AG11" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AH11" s="25">
         <v>7</v>
@@ -4776,39 +4808,39 @@
     <row r="12" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
+        <v>104</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="28"/>
       <c r="AH12" s="26">
         <f>SUM(AH7:AH11)</f>
       </c>
@@ -4823,388 +4855,328 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A13" s="57"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="59"/>
-      <c r="N13" s="59"/>
-      <c r="O13" s="59"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="59"/>
-      <c r="S13" s="59"/>
-      <c r="T13" s="59"/>
-      <c r="U13" s="59"/>
-      <c r="V13" s="59"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="59"/>
-      <c r="Y13" s="59"/>
-      <c r="Z13" s="59"/>
-      <c r="AA13" s="59"/>
-      <c r="AB13" s="59"/>
-      <c r="AC13" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD13" s="60"/>
-      <c r="AE13" s="60"/>
-      <c r="AF13" s="60"/>
-      <c r="AG13" s="60"/>
-      <c r="AH13" s="60"/>
-      <c r="AI13" s="60"/>
-      <c r="AJ13" s="60"/>
-      <c r="AK13" s="60"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="58"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="58"/>
+      <c r="V13" s="58"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="58"/>
+      <c r="Y13" s="58"/>
+      <c r="Z13" s="58"/>
+      <c r="AA13" s="58"/>
+      <c r="AB13" s="58"/>
+      <c r="AC13" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD13" s="59"/>
+      <c r="AE13" s="59"/>
+      <c r="AF13" s="59"/>
+      <c r="AG13" s="59"/>
+      <c r="AH13" s="59"/>
+      <c r="AI13" s="59"/>
+      <c r="AJ13" s="59"/>
+      <c r="AK13" s="59"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="52"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB14" s="63"/>
-      <c r="AC14" s="63"/>
-      <c r="AD14" s="63"/>
-      <c r="AE14" s="63"/>
-      <c r="AF14" s="63"/>
-      <c r="AG14" s="63"/>
-      <c r="AH14" s="63"/>
-      <c r="AI14" s="63"/>
-      <c r="AJ14" s="63"/>
-      <c r="AK14" s="63"/>
-    </row>
-    <row r="18" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="R18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG18" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH18" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI18" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ18" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK18" s="64" t="s">
-        <v>36</v>
+      <c r="A14" s="60"/>
+      <c r="B14" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="51"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="51"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="61"/>
+      <c r="Y14" s="61"/>
+      <c r="Z14" s="61"/>
+      <c r="AA14" s="62" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB14" s="62"/>
+      <c r="AC14" s="62"/>
+      <c r="AD14" s="62"/>
+      <c r="AE14" s="62"/>
+      <c r="AF14" s="62"/>
+      <c r="AG14" s="62"/>
+      <c r="AH14" s="62"/>
+      <c r="AI14" s="62"/>
+      <c r="AJ14" s="62"/>
+      <c r="AK14" s="62"/>
+    </row>
+    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA18" s="32" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A19" s="62"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="62"/>
-      <c r="R19" s="62"/>
-      <c r="S19" s="62"/>
-      <c r="T19" s="62"/>
-      <c r="U19" s="62"/>
-      <c r="V19" s="62"/>
-      <c r="W19" s="62"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
-      <c r="Z19" s="62"/>
-      <c r="AA19" s="52"/>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="52"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="52"/>
-      <c r="AF19" s="52"/>
-      <c r="AG19" s="52"/>
-      <c r="AH19" s="65"/>
-      <c r="AI19" s="65"/>
-      <c r="AJ19" s="65"/>
-      <c r="AK19" s="65"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="61"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="61"/>
+      <c r="T19" s="61"/>
+      <c r="U19" s="61"/>
+      <c r="V19" s="61"/>
+      <c r="W19" s="61"/>
+      <c r="X19" s="61"/>
+      <c r="Y19" s="61"/>
+      <c r="Z19" s="61"/>
+      <c r="AA19" s="51"/>
+      <c r="AB19" s="51"/>
+      <c r="AC19" s="51"/>
+      <c r="AD19" s="51"/>
+      <c r="AE19" s="51"/>
+      <c r="AF19" s="51"/>
+      <c r="AG19" s="51"/>
+      <c r="AH19" s="63"/>
+      <c r="AI19" s="63"/>
+      <c r="AJ19" s="63"/>
+      <c r="AK19" s="63"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A20" s="62"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="66" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="62"/>
-      <c r="S20" s="62"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="62"/>
-      <c r="W20" s="62"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="47"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="52"/>
-      <c r="AB20" s="52"/>
-      <c r="AC20" s="52"/>
-      <c r="AD20" s="52"/>
-      <c r="AE20" s="52"/>
-      <c r="AF20" s="52"/>
-      <c r="AG20" s="52"/>
-      <c r="AH20" s="65"/>
-      <c r="AI20" s="65"/>
-      <c r="AJ20" s="65"/>
-      <c r="AK20" s="65"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="61"/>
+      <c r="W20" s="61"/>
+      <c r="X20" s="61"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="61"/>
+      <c r="AA20" s="51"/>
+      <c r="AB20" s="51"/>
+      <c r="AC20" s="51"/>
+      <c r="AD20" s="51"/>
+      <c r="AE20" s="51"/>
+      <c r="AF20" s="51"/>
+      <c r="AG20" s="51"/>
+      <c r="AH20" s="63"/>
+      <c r="AI20" s="63"/>
+      <c r="AJ20" s="63"/>
+      <c r="AK20" s="63"/>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="66"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="47"/>
-      <c r="V21" s="47"/>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
-      <c r="AA21" s="47"/>
-      <c r="AB21" s="47"/>
-      <c r="AC21" s="47"/>
-      <c r="AD21" s="47"/>
-      <c r="AE21" s="47"/>
-      <c r="AF21" s="47"/>
-      <c r="AG21" s="47"/>
-      <c r="AH21" s="48"/>
-      <c r="AI21" s="67"/>
-      <c r="AJ21" s="68"/>
-      <c r="AK21" s="68"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="64"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="46"/>
+      <c r="U21" s="46"/>
+      <c r="V21" s="46"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="46"/>
+      <c r="Y21" s="46"/>
+      <c r="Z21" s="46"/>
+      <c r="AA21" s="46"/>
+      <c r="AB21" s="46"/>
+      <c r="AC21" s="46"/>
+      <c r="AD21" s="46"/>
+      <c r="AE21" s="46"/>
+      <c r="AF21" s="46"/>
+      <c r="AG21" s="46"/>
+      <c r="AH21" s="47"/>
+      <c r="AI21" s="65"/>
+      <c r="AJ21" s="66"/>
+      <c r="AK21" s="66"/>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="L22" s="66"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="47"/>
-      <c r="T22" s="47"/>
-      <c r="U22" s="47"/>
-      <c r="V22" s="47"/>
-      <c r="W22" s="47"/>
-      <c r="X22" s="47"/>
-      <c r="Y22" s="47"/>
-      <c r="Z22" s="47"/>
-      <c r="AA22" s="47"/>
-      <c r="AB22" s="47"/>
-      <c r="AC22" s="47"/>
-      <c r="AD22" s="47"/>
-      <c r="AE22" s="47"/>
-      <c r="AF22" s="47"/>
-      <c r="AG22" s="47"/>
-      <c r="AH22" s="48"/>
-      <c r="AI22" s="67"/>
-      <c r="AJ22" s="48"/>
-      <c r="AK22" s="48"/>
+      <c r="A22" s="46"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="L22" s="64"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="46"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
+      <c r="V22" s="46"/>
+      <c r="W22" s="46"/>
+      <c r="X22" s="46"/>
+      <c r="Y22" s="46"/>
+      <c r="Z22" s="46"/>
+      <c r="AA22" s="46"/>
+      <c r="AB22" s="46"/>
+      <c r="AC22" s="46"/>
+      <c r="AD22" s="46"/>
+      <c r="AE22" s="46"/>
+      <c r="AF22" s="46"/>
+      <c r="AG22" s="46"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="65"/>
+      <c r="AJ22" s="47"/>
+      <c r="AK22" s="47"/>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A23" s="69"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="56" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="47"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="52"/>
-      <c r="O23" s="52"/>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="52"/>
-      <c r="R23" s="52"/>
-      <c r="S23" s="52"/>
-      <c r="T23" s="52"/>
-      <c r="U23" s="52"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="47"/>
-      <c r="AA23" s="47"/>
-      <c r="AB23" s="47"/>
-      <c r="AC23" s="47"/>
-      <c r="AD23" s="47"/>
-      <c r="AE23" s="47"/>
-      <c r="AF23" s="47"/>
-      <c r="AG23" s="47"/>
-      <c r="AH23" s="48"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="48"/>
-      <c r="AK23" s="48"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" s="46"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="51"/>
+      <c r="R23" s="51"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="51"/>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46"/>
+      <c r="X23" s="46"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="46"/>
+      <c r="AA23" s="46"/>
+      <c r="AB23" s="46"/>
+      <c r="AC23" s="46"/>
+      <c r="AD23" s="46"/>
+      <c r="AE23" s="46"/>
+      <c r="AF23" s="46"/>
+      <c r="AG23" s="46"/>
+      <c r="AH23" s="47"/>
+      <c r="AI23" s="65"/>
+      <c r="AJ23" s="47"/>
+      <c r="AK23" s="47"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="47"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="47"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="66" t="s">
-        <v>78</v>
+      <c r="A24" s="46"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="46"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="64" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5243,43 +5215,43 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="73"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5287,45 +5259,45 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
-      <c r="W2" s="75"/>
-      <c r="X2" s="75"/>
-      <c r="Y2" s="75"/>
-      <c r="Z2" s="75"/>
-      <c r="AA2" s="75"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="75"/>
-      <c r="AD2" s="75"/>
-      <c r="AE2" s="75"/>
-      <c r="AF2" s="75"/>
-      <c r="AG2" s="75"/>
-      <c r="AH2" s="75"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
+      <c r="W2" s="73"/>
+      <c r="X2" s="73"/>
+      <c r="Y2" s="73"/>
+      <c r="Z2" s="73"/>
+      <c r="AA2" s="73"/>
+      <c r="AB2" s="73"/>
+      <c r="AC2" s="73"/>
+      <c r="AD2" s="73"/>
+      <c r="AE2" s="73"/>
+      <c r="AF2" s="73"/>
+      <c r="AG2" s="73"/>
+      <c r="AH2" s="73"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
       <c r="D3" s="3"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -5359,9 +5331,9 @@
       <c r="AH3" s="6"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="49"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="3"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -5395,444 +5367,387 @@
       <c r="AH4" s="6"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="79"/>
-      <c r="U5" s="79"/>
-      <c r="V5" s="79"/>
-      <c r="W5" s="79"/>
-      <c r="X5" s="79"/>
-      <c r="Y5" s="79"/>
-      <c r="Z5" s="79"/>
-      <c r="AA5" s="79"/>
-      <c r="AB5" s="79"/>
-      <c r="AC5" s="79"/>
-      <c r="AD5" s="79"/>
-      <c r="AE5" s="79"/>
-      <c r="AF5" s="79"/>
-      <c r="AG5" s="80"/>
-      <c r="AH5" s="81" t="s">
-        <v>81</v>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
+      <c r="W5" s="77"/>
+      <c r="X5" s="77"/>
+      <c r="Y5" s="77"/>
+      <c r="Z5" s="77"/>
+      <c r="AA5" s="77"/>
+      <c r="AB5" s="77"/>
+      <c r="AC5" s="77"/>
+      <c r="AD5" s="77"/>
+      <c r="AE5" s="77"/>
+      <c r="AF5" s="77"/>
+      <c r="AG5" s="78"/>
+      <c r="AH5" s="79" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="29.25" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="82">
+      <c r="A6" s="75"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="81" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="T6" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="U6" s="81" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W6" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X6" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y6" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z6" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA6" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB6" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC6" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD6" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE6" s="80" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF6" s="80" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG6" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH6" s="82"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" s="83">
         <v>1</v>
       </c>
-      <c r="D6" s="82">
-        <v>2</v>
-      </c>
-      <c r="E6" s="82">
-        <v>3</v>
-      </c>
-      <c r="F6" s="83">
-        <v>4</v>
-      </c>
-      <c r="G6" s="83">
-        <v>5</v>
-      </c>
-      <c r="H6" s="82">
-        <v>6</v>
-      </c>
-      <c r="I6" s="82">
-        <v>7</v>
-      </c>
-      <c r="J6" s="82">
-        <v>8</v>
-      </c>
-      <c r="K6" s="82">
-        <v>9</v>
-      </c>
-      <c r="L6" s="82">
-        <v>10</v>
-      </c>
-      <c r="M6" s="83">
-        <v>11</v>
-      </c>
-      <c r="N6" s="83">
-        <v>12</v>
-      </c>
-      <c r="O6" s="82">
-        <v>13</v>
-      </c>
-      <c r="P6" s="82">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="82">
-        <v>15</v>
-      </c>
-      <c r="R6" s="82">
-        <v>16</v>
-      </c>
-      <c r="S6" s="82">
-        <v>17</v>
-      </c>
-      <c r="T6" s="83">
-        <v>18</v>
-      </c>
-      <c r="U6" s="83">
-        <v>19</v>
-      </c>
-      <c r="V6" s="82">
-        <v>20</v>
-      </c>
-      <c r="W6" s="82">
-        <v>21</v>
-      </c>
-      <c r="X6" s="82">
-        <v>22</v>
-      </c>
-      <c r="Y6" s="82">
+      <c r="B7" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="R7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="S7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="T7" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="U7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="V7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="X7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z7" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA7" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD7" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH7" s="83">
         <v>23</v>
       </c>
-      <c r="Z6" s="82">
-        <v>24</v>
-      </c>
-      <c r="AA6" s="84">
-        <v>25</v>
-      </c>
-      <c r="AB6" s="84">
-        <v>26</v>
-      </c>
-      <c r="AC6" s="82">
-        <v>27</v>
-      </c>
-      <c r="AD6" s="82">
-        <v>28</v>
-      </c>
-      <c r="AE6" s="82">
-        <v>29</v>
-      </c>
-      <c r="AF6" s="82">
-        <v>30</v>
-      </c>
-      <c r="AG6" s="82">
-        <v>31</v>
-      </c>
-      <c r="AH6" s="85"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="86">
-        <v>1</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="88" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="88" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="88" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="88" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="R7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="S7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="T7" s="88" t="s">
-        <v>21</v>
-      </c>
-      <c r="U7" s="88" t="s">
-        <v>20</v>
-      </c>
-      <c r="V7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="W7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="X7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y7" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z7" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA7" s="89" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB7" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD7" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE7" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG7" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH7" s="86">
-        <v>23</v>
-      </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A8" s="90"/>
-      <c r="B8" s="91" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="91"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
-      <c r="N8" s="92"/>
-      <c r="O8" s="92"/>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="92"/>
-      <c r="S8" s="92"/>
-      <c r="T8" s="92"/>
-      <c r="U8" s="92"/>
-      <c r="V8" s="92"/>
-      <c r="W8" s="92"/>
-      <c r="X8" s="92"/>
-      <c r="Y8" s="92"/>
-      <c r="Z8" s="92"/>
-      <c r="AA8" s="92"/>
-      <c r="AB8" s="92"/>
-      <c r="AC8" s="92"/>
-      <c r="AD8" s="92"/>
-      <c r="AE8" s="92"/>
-      <c r="AF8" s="92"/>
-      <c r="AG8" s="92"/>
-      <c r="AH8" s="77">
+      <c r="A8" s="84"/>
+      <c r="B8" s="85" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="85"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="85"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
+      <c r="Z8" s="85"/>
+      <c r="AA8" s="85"/>
+      <c r="AB8" s="85"/>
+      <c r="AC8" s="85"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="85"/>
+      <c r="AF8" s="85"/>
+      <c r="AG8" s="85"/>
+      <c r="AH8" s="75">
         <f>SUM(AH7:AH7)</f>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:34" s="93" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="94"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="95"/>
-      <c r="O9" s="95"/>
-      <c r="P9" s="95"/>
-      <c r="Q9" s="95"/>
-      <c r="R9" s="95"/>
-      <c r="S9" s="95"/>
-      <c r="T9" s="95"/>
-      <c r="U9" s="95"/>
-      <c r="W9" s="96"/>
-      <c r="X9" s="96"/>
-      <c r="Y9" s="97" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z9" s="97"/>
-      <c r="AA9" s="97"/>
-      <c r="AB9" s="97"/>
-      <c r="AC9" s="97"/>
-      <c r="AD9" s="97"/>
-      <c r="AE9" s="97"/>
-      <c r="AF9" s="97"/>
-      <c r="AG9" s="97"/>
-      <c r="AH9" s="97"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:34" s="93" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="98"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
-      <c r="L10" s="101" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="101"/>
-      <c r="N10" s="101"/>
-      <c r="O10" s="101"/>
-      <c r="P10" s="101"/>
-      <c r="Q10" s="101"/>
-      <c r="R10" s="101"/>
-      <c r="S10" s="101"/>
-      <c r="T10" s="101"/>
-      <c r="U10" s="101"/>
-      <c r="V10" s="101"/>
-      <c r="W10" s="93"/>
-      <c r="X10" s="98"/>
-      <c r="Y10" s="102" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z10" s="102"/>
-      <c r="AA10" s="102"/>
-      <c r="AB10" s="102"/>
-      <c r="AC10" s="102"/>
-      <c r="AD10" s="102"/>
-      <c r="AE10" s="102"/>
-      <c r="AF10" s="102"/>
-      <c r="AG10" s="102"/>
-      <c r="AH10" s="102"/>
+    <row r="9" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="88"/>
+      <c r="L9" s="88"/>
+      <c r="M9" s="87"/>
+      <c r="N9" s="88"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="88"/>
+      <c r="Q9" s="88"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="W9" s="89"/>
+      <c r="X9" s="89"/>
+      <c r="Y9" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z9" s="90"/>
+      <c r="AA9" s="90"/>
+      <c r="AB9" s="90"/>
+      <c r="AC9" s="90"/>
+      <c r="AD9" s="90"/>
+      <c r="AE9" s="90"/>
+      <c r="AF9" s="90"/>
+      <c r="AG9" s="90"/>
+      <c r="AH9" s="90"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91"/>
+      <c r="B10" s="92" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="91"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="94"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
+      <c r="T10" s="94"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="94"/>
+      <c r="W10" s="86"/>
+      <c r="X10" s="91"/>
+      <c r="Y10" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z10" s="95"/>
+      <c r="AA10" s="95"/>
+      <c r="AB10" s="95"/>
+      <c r="AC10" s="95"/>
+      <c r="AD10" s="95"/>
+      <c r="AE10" s="95"/>
+      <c r="AF10" s="95"/>
+      <c r="AG10" s="95"/>
+      <c r="AH10" s="95"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="R14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V14" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH14" s="33" t="s">
-        <v>36</v>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B14" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y14" s="32" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="49"/>
+      <c r="B15" s="48"/>
       <c r="C15" s="1"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5842,44 +5757,44 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="103"/>
-      <c r="M15" s="103"/>
-      <c r="N15" s="103"/>
-      <c r="O15" s="103"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="103"/>
-      <c r="U15" s="103"/>
-      <c r="V15" s="103"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-      <c r="AA15" s="32"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="32"/>
-      <c r="AD15" s="32"/>
-      <c r="AE15" s="32"/>
-      <c r="AF15" s="32"/>
-      <c r="AG15" s="32"/>
-      <c r="AH15" s="32"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
+      <c r="S15" s="96"/>
+      <c r="T15" s="96"/>
+      <c r="U15" s="96"/>
+      <c r="V15" s="96"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31"/>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="31"/>
+      <c r="AE15" s="31"/>
+      <c r="AF15" s="31"/>
+      <c r="AG15" s="31"/>
+      <c r="AH15" s="31"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="104"/>
-      <c r="C16" s="105" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -5895,133 +5810,133 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-      <c r="AA16" s="103"/>
-      <c r="AB16" s="103"/>
-      <c r="AC16" s="103"/>
-      <c r="AD16" s="103"/>
-      <c r="AE16" s="103"/>
-      <c r="AF16" s="103"/>
-      <c r="AG16" s="103"/>
-      <c r="AH16" s="32"/>
+      <c r="AA16" s="96"/>
+      <c r="AB16" s="96"/>
+      <c r="AC16" s="96"/>
+      <c r="AD16" s="96"/>
+      <c r="AE16" s="96"/>
+      <c r="AF16" s="96"/>
+      <c r="AG16" s="96"/>
+      <c r="AH16" s="31"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="106"/>
-      <c r="C17" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="107"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="109"/>
-      <c r="K17" s="110" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" s="110"/>
-      <c r="M17" s="107"/>
-      <c r="N17" s="107"/>
-      <c r="O17" s="107"/>
-      <c r="P17" s="107"/>
-      <c r="Q17" s="107"/>
-      <c r="R17" s="107"/>
-      <c r="S17" s="107"/>
-      <c r="T17" s="109"/>
-      <c r="U17" s="109"/>
-      <c r="V17" s="107"/>
-      <c r="W17" s="107"/>
-      <c r="X17" s="107"/>
-      <c r="Y17" s="107"/>
-      <c r="Z17" s="107"/>
-      <c r="AA17" s="107"/>
-      <c r="AB17" s="107"/>
-      <c r="AC17" s="107"/>
-      <c r="AD17" s="110"/>
-      <c r="AE17" s="110"/>
-      <c r="AF17" s="107"/>
-      <c r="AG17" s="107"/>
-      <c r="AH17" s="32"/>
+      <c r="B17" s="99"/>
+      <c r="C17" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="103" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="103"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
+      <c r="T17" s="102"/>
+      <c r="U17" s="102"/>
+      <c r="V17" s="100"/>
+      <c r="W17" s="100"/>
+      <c r="X17" s="100"/>
+      <c r="Y17" s="100"/>
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="100"/>
+      <c r="AB17" s="100"/>
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="103"/>
+      <c r="AE17" s="103"/>
+      <c r="AF17" s="100"/>
+      <c r="AG17" s="100"/>
+      <c r="AH17" s="31"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="42"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="111"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="110" t="s">
-        <v>85</v>
-      </c>
-      <c r="L18" s="110"/>
-      <c r="M18" s="107"/>
-      <c r="N18" s="107"/>
-      <c r="O18" s="107"/>
-      <c r="P18" s="107"/>
-      <c r="Q18" s="107"/>
-      <c r="R18" s="107"/>
-      <c r="S18" s="107"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="107"/>
-      <c r="W18" s="107"/>
-      <c r="X18" s="107"/>
-      <c r="Y18" s="107"/>
-      <c r="Z18" s="107"/>
-      <c r="AA18" s="107"/>
-      <c r="AB18" s="107"/>
-      <c r="AC18" s="107"/>
-      <c r="AD18" s="110"/>
-      <c r="AE18" s="110"/>
-      <c r="AF18" s="107"/>
-      <c r="AG18" s="107"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="101"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="103" t="s">
+        <v>116</v>
+      </c>
+      <c r="L18" s="103"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="102"/>
+      <c r="U18" s="102"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="103"/>
+      <c r="AE18" s="103"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
       <c r="AH18" s="6"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="42"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="110" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="110"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="107"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="107"/>
-      <c r="T19" s="109"/>
-      <c r="U19" s="109"/>
-      <c r="V19" s="107"/>
-      <c r="W19" s="107"/>
-      <c r="X19" s="107"/>
-      <c r="Y19" s="107"/>
-      <c r="Z19" s="107"/>
-      <c r="AA19" s="107"/>
-      <c r="AB19" s="107"/>
-      <c r="AC19" s="107"/>
-      <c r="AD19" s="110"/>
-      <c r="AE19" s="110"/>
-      <c r="AF19" s="107"/>
-      <c r="AG19" s="107"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="103" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="103"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="102"/>
+      <c r="U19" s="102"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="100"/>
+      <c r="AB19" s="100"/>
+      <c r="AC19" s="100"/>
+      <c r="AD19" s="103"/>
+      <c r="AE19" s="103"/>
+      <c r="AF19" s="100"/>
+      <c r="AG19" s="100"/>
       <c r="AH19" s="6"/>
     </row>
   </sheetData>
@@ -6060,94 +5975,94 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="73" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="73"/>
+      <c r="A1" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="75" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75"/>
-      <c r="V2" s="75"/>
-      <c r="W2" s="75"/>
-      <c r="X2" s="75"/>
-      <c r="Y2" s="75"/>
-      <c r="Z2" s="75"/>
-      <c r="AA2" s="75"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="75"/>
-      <c r="AD2" s="75"/>
-      <c r="AE2" s="75"/>
-      <c r="AF2" s="75"/>
-      <c r="AG2" s="75"/>
-      <c r="AH2" s="75"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
+      <c r="W2" s="73"/>
+      <c r="X2" s="73"/>
+      <c r="Y2" s="73"/>
+      <c r="Z2" s="73"/>
+      <c r="AA2" s="73"/>
+      <c r="AB2" s="73"/>
+      <c r="AC2" s="73"/>
+      <c r="AD2" s="73"/>
+      <c r="AE2" s="73"/>
+      <c r="AF2" s="73"/>
+      <c r="AG2" s="73"/>
+      <c r="AH2" s="73"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -6178,9 +6093,9 @@
       <c r="AH3" s="6"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="49"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="3"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -6214,52 +6129,52 @@
       <c r="AH4" s="6"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="112" t="s">
+      <c r="C5" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="113"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="113"/>
-      <c r="W5" s="113"/>
-      <c r="X5" s="113"/>
-      <c r="Y5" s="113"/>
-      <c r="Z5" s="113"/>
-      <c r="AA5" s="113"/>
-      <c r="AB5" s="113"/>
-      <c r="AC5" s="113"/>
-      <c r="AD5" s="113"/>
-      <c r="AE5" s="113"/>
-      <c r="AF5" s="113"/>
-      <c r="AG5" s="114"/>
-      <c r="AH5" s="81" t="s">
-        <v>81</v>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="106"/>
+      <c r="S5" s="106"/>
+      <c r="T5" s="106"/>
+      <c r="U5" s="106"/>
+      <c r="V5" s="106"/>
+      <c r="W5" s="106"/>
+      <c r="X5" s="106"/>
+      <c r="Y5" s="106"/>
+      <c r="Z5" s="106"/>
+      <c r="AA5" s="106"/>
+      <c r="AB5" s="106"/>
+      <c r="AC5" s="106"/>
+      <c r="AD5" s="106"/>
+      <c r="AE5" s="106"/>
+      <c r="AF5" s="106"/>
+      <c r="AG5" s="107"/>
+      <c r="AH5" s="79" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="75"/>
       <c r="C6" s="16">
         <v>1</v>
       </c>
@@ -6353,343 +6268,348 @@
       <c r="AG6" s="16">
         <v>31</v>
       </c>
-      <c r="AH6" s="85"/>
+      <c r="AH6" s="82"/>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" s="77"/>
-      <c r="B7" s="115" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="23"/>
-      <c r="AE7" s="23"/>
-      <c r="AF7" s="23"/>
-      <c r="AG7" s="23"/>
-      <c r="AH7" s="85"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="T7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="U7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="V7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="X7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y7" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z7" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA7" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB7" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC7" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD7" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG7" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH7" s="82"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A8" s="86">
+      <c r="A8" s="83">
         <v>1</v>
       </c>
-      <c r="B8" s="116" t="s">
-        <v>18</v>
+      <c r="B8" s="109" t="s">
+        <v>49</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="U8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Y8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="Z8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AC8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AE8" s="23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AF8" s="23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AG8" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH8" s="86">
+        <v>50</v>
+      </c>
+      <c r="AH8" s="83">
         <v>25</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="92"/>
-      <c r="R9" s="92"/>
-      <c r="S9" s="92"/>
-      <c r="T9" s="92"/>
-      <c r="U9" s="92"/>
-      <c r="V9" s="92"/>
-      <c r="W9" s="92"/>
-      <c r="X9" s="92"/>
-      <c r="Y9" s="92"/>
-      <c r="Z9" s="92"/>
-      <c r="AA9" s="92"/>
-      <c r="AB9" s="92"/>
-      <c r="AC9" s="92"/>
-      <c r="AD9" s="92"/>
-      <c r="AE9" s="92"/>
-      <c r="AF9" s="92"/>
-      <c r="AG9" s="92"/>
-      <c r="AH9" s="77">
+      <c r="A9" s="84"/>
+      <c r="B9" s="85" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="85"/>
+      <c r="Q9" s="85"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="85"/>
+      <c r="T9" s="85"/>
+      <c r="U9" s="85"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="85"/>
+      <c r="X9" s="85"/>
+      <c r="Y9" s="85"/>
+      <c r="Z9" s="85"/>
+      <c r="AA9" s="85"/>
+      <c r="AB9" s="85"/>
+      <c r="AC9" s="85"/>
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="85"/>
+      <c r="AF9" s="85"/>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="75">
         <f>SUM(AH8:AH8)</f>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:34" s="93" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="94"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="95"/>
-      <c r="O10" s="95"/>
-      <c r="P10" s="95"/>
-      <c r="Q10" s="95"/>
-      <c r="R10" s="95"/>
-      <c r="S10" s="95"/>
-      <c r="T10" s="95"/>
-      <c r="U10" s="95"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="96"/>
-      <c r="Y10" s="97" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z10" s="97"/>
-      <c r="AA10" s="97"/>
-      <c r="AB10" s="97"/>
-      <c r="AC10" s="97"/>
-      <c r="AD10" s="97"/>
-      <c r="AE10" s="97"/>
-      <c r="AF10" s="97"/>
-      <c r="AG10" s="97"/>
-      <c r="AH10" s="97"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:34" s="93" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="98"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="101" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="101"/>
-      <c r="N11" s="101"/>
-      <c r="O11" s="101"/>
-      <c r="P11" s="101"/>
-      <c r="Q11" s="101"/>
-      <c r="R11" s="101"/>
-      <c r="S11" s="101"/>
-      <c r="T11" s="101"/>
-      <c r="U11" s="101"/>
-      <c r="V11" s="101"/>
-      <c r="W11" s="93"/>
-      <c r="X11" s="98"/>
-      <c r="Y11" s="102" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z11" s="102"/>
-      <c r="AA11" s="102"/>
-      <c r="AB11" s="102"/>
-      <c r="AC11" s="102"/>
-      <c r="AD11" s="102"/>
-      <c r="AE11" s="102"/>
-      <c r="AF11" s="102"/>
-      <c r="AG11" s="102"/>
-      <c r="AH11" s="102"/>
+    <row r="10" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="88"/>
+      <c r="L10" s="88"/>
+      <c r="M10" s="87"/>
+      <c r="N10" s="88"/>
+      <c r="O10" s="88"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="88"/>
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="W10" s="89"/>
+      <c r="X10" s="89"/>
+      <c r="Y10" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z10" s="90"/>
+      <c r="AA10" s="90"/>
+      <c r="AB10" s="90"/>
+      <c r="AC10" s="90"/>
+      <c r="AD10" s="90"/>
+      <c r="AE10" s="90"/>
+      <c r="AF10" s="90"/>
+      <c r="AG10" s="90"/>
+      <c r="AH10" s="90"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="91"/>
+      <c r="B11" s="92" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="91"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="94"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
+      <c r="T11" s="94"/>
+      <c r="U11" s="94"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="86"/>
+      <c r="X11" s="91"/>
+      <c r="Y11" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z11" s="95"/>
+      <c r="AA11" s="95"/>
+      <c r="AB11" s="95"/>
+      <c r="AC11" s="95"/>
+      <c r="AD11" s="95"/>
+      <c r="AE11" s="95"/>
+      <c r="AF11" s="95"/>
+      <c r="AG11" s="95"/>
+      <c r="AH11" s="95"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="P15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="R15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="S15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="T15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="U15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="V15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH15" s="33" t="s">
-        <v>36</v>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B15" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y15" s="32" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="49"/>
+      <c r="B16" s="48"/>
       <c r="C16" s="1"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6699,42 +6619,42 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="103"/>
-      <c r="M16" s="103"/>
-      <c r="N16" s="103"/>
-      <c r="O16" s="103"/>
-      <c r="P16" s="103"/>
-      <c r="Q16" s="103"/>
-      <c r="R16" s="103"/>
-      <c r="S16" s="103"/>
-      <c r="T16" s="103"/>
-      <c r="U16" s="103"/>
-      <c r="V16" s="103"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="32"/>
-      <c r="AD16" s="32"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="32"/>
-      <c r="AG16" s="32"/>
-      <c r="AH16" s="32"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="96"/>
+      <c r="U16" s="96"/>
+      <c r="V16" s="96"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="31"/>
+      <c r="AE16" s="31"/>
+      <c r="AF16" s="31"/>
+      <c r="AG16" s="31"/>
+      <c r="AH16" s="31"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="104"/>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="98"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -6750,121 +6670,121 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="103"/>
-      <c r="AB17" s="103"/>
-      <c r="AC17" s="103"/>
-      <c r="AD17" s="103"/>
-      <c r="AE17" s="103"/>
-      <c r="AF17" s="103"/>
-      <c r="AG17" s="103"/>
-      <c r="AH17" s="32"/>
+      <c r="AA17" s="96"/>
+      <c r="AB17" s="96"/>
+      <c r="AC17" s="96"/>
+      <c r="AD17" s="96"/>
+      <c r="AE17" s="96"/>
+      <c r="AF17" s="96"/>
+      <c r="AG17" s="96"/>
+      <c r="AH17" s="31"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="106"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="107"/>
-      <c r="N18" s="107"/>
-      <c r="O18" s="107"/>
-      <c r="P18" s="107"/>
-      <c r="Q18" s="107"/>
-      <c r="R18" s="107"/>
-      <c r="S18" s="107"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="107"/>
-      <c r="W18" s="107"/>
-      <c r="X18" s="107"/>
-      <c r="Y18" s="107"/>
-      <c r="Z18" s="107"/>
-      <c r="AA18" s="107"/>
-      <c r="AB18" s="107"/>
-      <c r="AC18" s="107"/>
-      <c r="AD18" s="110"/>
-      <c r="AE18" s="110"/>
-      <c r="AF18" s="107"/>
-      <c r="AG18" s="107"/>
-      <c r="AH18" s="32"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="101"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="102"/>
+      <c r="U18" s="102"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="103"/>
+      <c r="AE18" s="103"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
+      <c r="AH18" s="31"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="42"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="107"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="107"/>
-      <c r="T19" s="109"/>
-      <c r="U19" s="109"/>
-      <c r="V19" s="107"/>
-      <c r="W19" s="107"/>
-      <c r="X19" s="107"/>
-      <c r="Y19" s="107"/>
-      <c r="Z19" s="107"/>
-      <c r="AA19" s="107"/>
-      <c r="AB19" s="107"/>
-      <c r="AC19" s="107"/>
-      <c r="AD19" s="110"/>
-      <c r="AE19" s="110"/>
-      <c r="AF19" s="107"/>
-      <c r="AG19" s="107"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="103"/>
+      <c r="L19" s="103"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="100"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="102"/>
+      <c r="U19" s="102"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="100"/>
+      <c r="AB19" s="100"/>
+      <c r="AC19" s="100"/>
+      <c r="AD19" s="103"/>
+      <c r="AE19" s="103"/>
+      <c r="AF19" s="100"/>
+      <c r="AG19" s="100"/>
       <c r="AH19" s="6"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="108"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="107"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="107"/>
-      <c r="P20" s="107"/>
-      <c r="Q20" s="107"/>
-      <c r="R20" s="107"/>
-      <c r="S20" s="107"/>
-      <c r="T20" s="109"/>
-      <c r="U20" s="109"/>
-      <c r="V20" s="107"/>
-      <c r="W20" s="107"/>
-      <c r="X20" s="107"/>
-      <c r="Y20" s="107"/>
-      <c r="Z20" s="107"/>
-      <c r="AA20" s="107"/>
-      <c r="AB20" s="107"/>
-      <c r="AC20" s="107"/>
-      <c r="AD20" s="110"/>
-      <c r="AE20" s="110"/>
-      <c r="AF20" s="107"/>
-      <c r="AG20" s="107"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="100"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="102"/>
+      <c r="U20" s="102"/>
+      <c r="V20" s="100"/>
+      <c r="W20" s="100"/>
+      <c r="X20" s="100"/>
+      <c r="Y20" s="100"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="100"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="100"/>
+      <c r="AD20" s="103"/>
+      <c r="AE20" s="103"/>
+      <c r="AF20" s="100"/>
+      <c r="AG20" s="100"/>
       <c r="AH20" s="6"/>
     </row>
   </sheetData>

--- a/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
+++ b/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="117">
   <si>
     <r>
       <t xml:space="preserve">Đơn vị: </t>
@@ -262,127 +262,121 @@
     <t>Hải Vân, ngày 31 tháng 07 năm 2026</t>
   </si>
   <si>
+    <t>Bác sĩ Nguyễn Văn Trưởng</t>
+  </si>
+  <si>
+    <t>Ký hiệu chấm công:</t>
+  </si>
+  <si>
+    <t>Lương Thời gian</t>
+  </si>
+  <si>
+    <t>Hội nghị, học tập</t>
+  </si>
+  <si>
+    <t>Nghỉ ốm</t>
+  </si>
+  <si>
+    <t>Ô</t>
+  </si>
+  <si>
+    <t>Công tác</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>Con ốm</t>
+  </si>
+  <si>
+    <t>Cô</t>
+  </si>
+  <si>
+    <t>Trực</t>
+  </si>
+  <si>
+    <t>Thai sản</t>
+  </si>
+  <si>
+    <t>Ts</t>
+  </si>
+  <si>
+    <t>Trực dịch</t>
+  </si>
+  <si>
+    <t>Td</t>
+  </si>
+  <si>
+    <t>Nghỉ không lương</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Chống dịch</t>
+  </si>
+  <si>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>Nghỉ Phép</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Bù lễ</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>Trực tiêm chủng</t>
+  </si>
+  <si>
+    <t>TTc</t>
+  </si>
+  <si>
+    <t>Phép chế độ</t>
+  </si>
+  <si>
+    <t>Pcđ</t>
+  </si>
+  <si>
+    <t>Tiêm chủng</t>
+  </si>
+  <si>
+    <t>Đơn vị: Trạm Y tế phường Hải Vân</t>
+  </si>
+  <si>
+    <t>BẢNG CHẤM CÔNG TRỰC</t>
+  </si>
+  <si>
+    <t>Tháng 07 Năm 2026</t>
+  </si>
+  <si>
+    <t>Mã đơn vị QHN:……………….</t>
+  </si>
+  <si>
+    <t>Tổng số ngày trong tháng</t>
+  </si>
+  <si>
+    <t>Ngày thường</t>
+  </si>
+  <si>
+    <t>Ngày thứ bảy, CN</t>
+  </si>
+  <si>
+    <t>Ngày Lễ</t>
+  </si>
+  <si>
+    <t>Tổng cộng</t>
+  </si>
+  <si>
+    <t>Tổng cộng: 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Người chấm công</t>
-  </si>
-  <si>
-    <t>Phụ trách bộ phận</t>
-  </si>
-  <si>
-    <t>Trưởng khoa</t>
-  </si>
-  <si>
-    <t>Bác sĩ Nguyễn Văn Trưởng</t>
-  </si>
-  <si>
-    <t>Ký hiệu chấm công:</t>
-  </si>
-  <si>
-    <t>Lương Thời gian</t>
-  </si>
-  <si>
-    <t>Hội nghị, học tập</t>
-  </si>
-  <si>
-    <t>Nghỉ ốm</t>
-  </si>
-  <si>
-    <t>Ô</t>
-  </si>
-  <si>
-    <t>Công tác</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>Con ốm</t>
-  </si>
-  <si>
-    <t>Cô</t>
-  </si>
-  <si>
-    <t>Trực</t>
-  </si>
-  <si>
-    <t>Thai sản</t>
-  </si>
-  <si>
-    <t>Ts</t>
-  </si>
-  <si>
-    <t>Trực dịch</t>
-  </si>
-  <si>
-    <t>Td</t>
-  </si>
-  <si>
-    <t>Nghỉ không lương</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Chống dịch</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>Nghỉ Phép</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Bù lễ</t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>Trực tiêm chủng</t>
-  </si>
-  <si>
-    <t>TTc</t>
-  </si>
-  <si>
-    <t>Phép chế độ</t>
-  </si>
-  <si>
-    <t>Pcđ</t>
-  </si>
-  <si>
-    <t>Tiêm chủng</t>
-  </si>
-  <si>
-    <t>Đơn vị: Trạm Y tế phường Hải Vân</t>
-  </si>
-  <si>
-    <t>BẢNG CHẤM CÔNG TRỰC</t>
-  </si>
-  <si>
-    <t>Tháng 07 Năm 2026</t>
-  </si>
-  <si>
-    <t>Mã đơn vị QHN:……………….</t>
-  </si>
-  <si>
-    <t>Tổng số ngày trong tháng</t>
-  </si>
-  <si>
-    <t>Ngày thường</t>
-  </si>
-  <si>
-    <t>Ngày thứ bảy, CN</t>
-  </si>
-  <si>
-    <t>Ngày Lễ</t>
-  </si>
-  <si>
-    <t>Tổng cộng</t>
-  </si>
-  <si>
-    <t>Tổng cộng: 5</t>
   </si>
   <si>
     <t>24h</t>
@@ -606,8 +600,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFE2E2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -3396,13 +3389,27 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
+      <c r="T16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="W16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="X16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z16" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="AA16" s="30" t="s">
         <v>63</v>
       </c>
@@ -3421,7 +3428,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="3"/>
@@ -3434,7 +3441,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="31" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="M17" s="31"/>
       <c r="N17" s="31"/>
@@ -3451,7 +3458,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="31" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="AB17" s="31"/>
       <c r="AC17" s="31"/>
@@ -3475,14 +3482,14 @@
         <v>58</v>
       </c>
       <c r="AA21" s="32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="33" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33"/>
@@ -3525,7 +3532,7 @@
       <c r="A23" s="35"/>
       <c r="B23" s="36"/>
       <c r="C23" s="37" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D23" s="37"/>
       <c r="E23" s="37"/>
@@ -3548,7 +3555,7 @@
       <c r="T23" s="39"/>
       <c r="U23" s="39"/>
       <c r="V23" s="39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="W23" s="39"/>
       <c r="X23" s="39"/>
@@ -3574,7 +3581,7 @@
       <c r="A24" s="41"/>
       <c r="B24" s="39"/>
       <c r="C24" s="42" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="42"/>
@@ -3584,7 +3591,7 @@
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
       <c r="K24" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L24" s="38"/>
       <c r="M24" s="39"/>
@@ -3597,7 +3604,7 @@
       <c r="T24" s="39"/>
       <c r="U24" s="39"/>
       <c r="V24" s="39" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="W24" s="39"/>
       <c r="X24" s="39"/>
@@ -3605,7 +3612,7 @@
       <c r="Z24" s="39"/>
       <c r="AA24" s="39"/>
       <c r="AB24" s="39" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AC24" s="39"/>
       <c r="AD24" s="39"/>
@@ -3623,7 +3630,7 @@
       <c r="A25" s="41"/>
       <c r="B25" s="39"/>
       <c r="C25" s="37" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -3633,7 +3640,7 @@
       <c r="I25" s="37"/>
       <c r="J25" s="37"/>
       <c r="K25" s="38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L25" s="38"/>
       <c r="M25" s="39"/>
@@ -3646,7 +3653,7 @@
       <c r="T25" s="39"/>
       <c r="U25" s="39"/>
       <c r="V25" s="39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="W25" s="39"/>
       <c r="X25" s="39"/>
@@ -3672,7 +3679,7 @@
       <c r="A26" s="41"/>
       <c r="B26" s="39"/>
       <c r="C26" s="37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -3682,7 +3689,7 @@
       <c r="I26" s="37"/>
       <c r="J26" s="37"/>
       <c r="K26" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L26" s="38"/>
       <c r="M26" s="39"/>
@@ -3721,7 +3728,7 @@
       <c r="A27" s="41"/>
       <c r="B27" s="39"/>
       <c r="C27" s="37" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="37"/>
@@ -3731,7 +3738,7 @@
       <c r="I27" s="37"/>
       <c r="J27" s="37"/>
       <c r="K27" s="38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L27" s="38"/>
       <c r="M27" s="39"/>
@@ -3744,7 +3751,7 @@
       <c r="T27" s="39"/>
       <c r="U27" s="39"/>
       <c r="V27" s="39" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="W27" s="39"/>
       <c r="X27" s="39"/>
@@ -3752,7 +3759,7 @@
       <c r="Z27" s="39"/>
       <c r="AA27" s="39"/>
       <c r="AB27" s="38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AC27" s="38"/>
       <c r="AD27" s="39"/>
@@ -3770,7 +3777,7 @@
       <c r="A28" s="44"/>
       <c r="B28" s="38"/>
       <c r="C28" s="42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D28" s="42"/>
       <c r="E28" s="42"/>
@@ -3780,7 +3787,7 @@
       <c r="I28" s="42"/>
       <c r="J28" s="42"/>
       <c r="K28" s="38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L28" s="38"/>
       <c r="M28" s="38"/>
@@ -3793,7 +3800,7 @@
       <c r="T28" s="38"/>
       <c r="U28" s="38"/>
       <c r="V28" s="39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="W28" s="39"/>
       <c r="X28" s="39"/>
@@ -3801,7 +3808,7 @@
       <c r="Z28" s="39"/>
       <c r="AA28" s="39"/>
       <c r="AB28" s="38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AC28" s="38"/>
       <c r="AD28" s="39"/>
@@ -3818,7 +3825,7 @@
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="41"/>
       <c r="C29" s="39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
@@ -3828,7 +3835,7 @@
       <c r="I29" s="37"/>
       <c r="J29" s="37"/>
       <c r="K29" s="37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L29" s="39"/>
       <c r="M29" s="39"/>
@@ -3841,7 +3848,7 @@
       <c r="T29" s="39"/>
       <c r="U29" s="39"/>
       <c r="V29" s="39" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="W29" s="39"/>
       <c r="X29" s="39"/>
@@ -3849,7 +3856,7 @@
       <c r="Z29" s="39"/>
       <c r="AA29" s="39"/>
       <c r="AB29" s="39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AC29" s="39"/>
       <c r="AD29" s="41"/>
@@ -3860,13 +3867,13 @@
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C30" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K30" s="39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="V30" s="39" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="W30" s="39"/>
       <c r="X30" s="39"/>
@@ -3932,7 +3939,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="48" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -3942,7 +3949,7 @@
       <c r="G1" s="48"/>
       <c r="H1" s="48"/>
       <c r="I1" s="49" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1" s="49"/>
       <c r="K1" s="49"/>
@@ -3985,7 +3992,7 @@
       <c r="G2" s="50"/>
       <c r="H2" s="50"/>
       <c r="I2" s="51" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J2" s="51"/>
       <c r="K2" s="51"/>
@@ -4018,7 +4025,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:37" s="52" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -4137,7 +4144,7 @@
       <c r="AF5" s="14"/>
       <c r="AG5" s="15"/>
       <c r="AH5" s="13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AI5" s="14"/>
       <c r="AJ5" s="14"/>
@@ -4240,16 +4247,16 @@
         <v>42</v>
       </c>
       <c r="AH6" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI6" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ6" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK6" s="19" t="s">
         <v>100</v>
-      </c>
-      <c r="AI6" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ6" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK6" s="19" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
@@ -4808,7 +4815,7 @@
     <row r="12" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
@@ -4874,15 +4881,33 @@
       <c r="Q13" s="58"/>
       <c r="R13" s="58"/>
       <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="58"/>
-      <c r="X13" s="58"/>
-      <c r="Y13" s="58"/>
-      <c r="Z13" s="58"/>
-      <c r="AA13" s="58"/>
-      <c r="AB13" s="58"/>
+      <c r="T13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="U13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="V13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="W13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="X13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA13" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB13" s="58" t="s">
+        <v>51</v>
+      </c>
       <c r="AC13" s="59" t="s">
         <v>63</v>
       </c>
@@ -4898,7 +4923,7 @@
     <row r="14" ht="15.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" s="60"/>
       <c r="B14" s="50" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C14" s="61"/>
       <c r="D14" s="61"/>
@@ -4910,7 +4935,7 @@
       <c r="J14" s="61"/>
       <c r="K14" s="61"/>
       <c r="L14" s="51" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="M14" s="51"/>
       <c r="N14" s="51"/>
@@ -4927,7 +4952,7 @@
       <c r="Y14" s="61"/>
       <c r="Z14" s="61"/>
       <c r="AA14" s="62" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="AB14" s="62"/>
       <c r="AC14" s="62"/>
@@ -4948,7 +4973,7 @@
         <v>58</v>
       </c>
       <c r="AA18" s="32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.25">
@@ -4994,7 +5019,7 @@
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
       <c r="C20" s="64" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="64"/>
@@ -5035,11 +5060,11 @@
       <c r="A21" s="46"/>
       <c r="B21" s="46"/>
       <c r="C21" s="46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D21" s="46"/>
       <c r="E21" s="46" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F21" s="46"/>
       <c r="G21" s="46"/>
@@ -5080,7 +5105,7 @@
       <c r="A22" s="46"/>
       <c r="B22" s="46"/>
       <c r="C22" s="46" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D22" s="46"/>
       <c r="E22" s="46"/>
@@ -5090,7 +5115,7 @@
       <c r="I22" s="46"/>
       <c r="J22" s="46"/>
       <c r="K22" s="64" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L22" s="64"/>
       <c r="M22" s="46"/>
@@ -5123,7 +5148,7 @@
       <c r="A23" s="67"/>
       <c r="B23" s="67"/>
       <c r="C23" s="55" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D23" s="46"/>
       <c r="E23" s="46"/>
@@ -5166,7 +5191,7 @@
       <c r="A24" s="46"/>
       <c r="B24" s="68"/>
       <c r="C24" s="64" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D24" s="46"/>
       <c r="E24" s="64"/>
@@ -5176,7 +5201,7 @@
       <c r="I24" s="64"/>
       <c r="J24" s="46"/>
       <c r="K24" s="64" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -5205,7 +5230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.5703125" customWidth="1"/>
@@ -5215,7 +5240,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5223,7 +5248,7 @@
       <c r="E1" s="69"/>
       <c r="F1" s="70"/>
       <c r="G1" s="71" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H1" s="71"/>
       <c r="I1" s="71"/>
@@ -5262,7 +5287,7 @@
       <c r="E2" s="72"/>
       <c r="F2" s="72"/>
       <c r="G2" s="73" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H2" s="73"/>
       <c r="I2" s="73"/>
@@ -5407,7 +5432,7 @@
       <c r="AF5" s="77"/>
       <c r="AG5" s="78"/>
       <c r="AH5" s="79" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" ht="29.25" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -5615,7 +5640,7 @@
     <row r="8" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C8" s="85"/>
       <c r="D8" s="85"/>
@@ -5652,7 +5677,7 @@
         <f>SUM(AH7:AH7)</f>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:35" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="87"/>
       <c r="B9" s="87"/>
       <c r="C9" s="87"/>
@@ -5672,10 +5697,21 @@
       <c r="Q9" s="88"/>
       <c r="R9" s="88"/>
       <c r="S9" s="88"/>
-      <c r="T9" s="88"/>
-      <c r="U9" s="88"/>
-      <c r="W9" s="89"/>
-      <c r="X9" s="89"/>
+      <c r="T9" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="U9" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="V9" s="86" t="s">
+        <v>51</v>
+      </c>
+      <c r="W9" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="X9" s="89" t="s">
+        <v>51</v>
+      </c>
       <c r="Y9" s="90" t="s">
         <v>63</v>
       </c>
@@ -5688,11 +5724,14 @@
       <c r="AF9" s="90"/>
       <c r="AG9" s="90"/>
       <c r="AH9" s="90"/>
+      <c r="AI9" s="86" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="91"/>
       <c r="B10" s="92" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C10" s="91"/>
       <c r="D10" s="93"/>
@@ -5704,7 +5743,7 @@
       <c r="J10" s="93"/>
       <c r="K10" s="93"/>
       <c r="L10" s="94" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="M10" s="94"/>
       <c r="N10" s="94"/>
@@ -5719,7 +5758,7 @@
       <c r="W10" s="86"/>
       <c r="X10" s="91"/>
       <c r="Y10" s="95" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="Z10" s="95"/>
       <c r="AA10" s="95"/>
@@ -5742,7 +5781,7 @@
         <v>58</v>
       </c>
       <c r="Y14" s="32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -5785,7 +5824,7 @@
       <c r="A16" s="1"/>
       <c r="B16" s="97"/>
       <c r="C16" s="98" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D16" s="98"/>
       <c r="E16" s="98"/>
@@ -5823,7 +5862,7 @@
       <c r="A17" s="1"/>
       <c r="B17" s="99"/>
       <c r="C17" s="41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D17" s="100"/>
       <c r="E17" s="100"/>
@@ -5863,7 +5902,7 @@
       <c r="A18" s="41"/>
       <c r="B18" s="69"/>
       <c r="C18" s="41" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D18" s="100"/>
       <c r="E18" s="100"/>
@@ -5873,7 +5912,7 @@
       <c r="I18" s="102"/>
       <c r="J18" s="102"/>
       <c r="K18" s="103" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L18" s="103"/>
       <c r="M18" s="100"/>
@@ -5903,7 +5942,7 @@
       <c r="A19" s="41"/>
       <c r="B19" s="69"/>
       <c r="C19" s="41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D19" s="100"/>
       <c r="E19" s="100"/>
@@ -5966,7 +6005,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH20"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.85546875" customWidth="1"/>
@@ -5976,7 +6015,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="48" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -5984,7 +6023,7 @@
       <c r="E1" s="48"/>
       <c r="F1" s="48"/>
       <c r="G1" s="71" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H1" s="71"/>
       <c r="I1" s="71"/>
@@ -6024,7 +6063,7 @@
       <c r="E2" s="48"/>
       <c r="F2" s="48"/>
       <c r="G2" s="73" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H2" s="73"/>
       <c r="I2" s="73"/>
@@ -6169,7 +6208,7 @@
       <c r="AF5" s="106"/>
       <c r="AG5" s="107"/>
       <c r="AH5" s="79" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -6273,7 +6312,7 @@
     <row r="7" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="75"/>
       <c r="B7" s="108" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>12</v>
@@ -6477,7 +6516,7 @@
     <row r="9" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" s="84"/>
       <c r="B9" s="85" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -6514,7 +6553,7 @@
         <f>SUM(AH8:AH8)</f>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" spans="1:35" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="87"/>
       <c r="B10" s="87"/>
       <c r="C10" s="87"/>
@@ -6534,10 +6573,21 @@
       <c r="Q10" s="88"/>
       <c r="R10" s="88"/>
       <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="U10" s="88"/>
-      <c r="W10" s="89"/>
-      <c r="X10" s="89"/>
+      <c r="T10" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="V10" s="86" t="s">
+        <v>51</v>
+      </c>
+      <c r="W10" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="X10" s="89" t="s">
+        <v>51</v>
+      </c>
       <c r="Y10" s="90" t="s">
         <v>63</v>
       </c>
@@ -6550,11 +6600,14 @@
       <c r="AF10" s="90"/>
       <c r="AG10" s="90"/>
       <c r="AH10" s="90"/>
+      <c r="AI10" s="86" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="91"/>
       <c r="B11" s="92" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C11" s="91"/>
       <c r="D11" s="93"/>
@@ -6566,7 +6619,7 @@
       <c r="J11" s="93"/>
       <c r="K11" s="93"/>
       <c r="L11" s="94" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="M11" s="94"/>
       <c r="N11" s="94"/>
@@ -6581,7 +6634,7 @@
       <c r="W11" s="86"/>
       <c r="X11" s="91"/>
       <c r="Y11" s="95" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="Z11" s="95"/>
       <c r="AA11" s="95"/>
@@ -6604,7 +6657,7 @@
         <v>58</v>
       </c>
       <c r="Y15" s="32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">

--- a/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
+++ b/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="90">
   <si>
     <r>
       <t xml:space="preserve">Đơn vị: </t>
@@ -32,13 +32,7 @@
     </r>
   </si>
   <si>
-    <t>Mẫu C01-HD</t>
-  </si>
-  <si>
     <t>Bộ phận: Khoa Dược-Thiết bị y tế và Cận lâm sàng</t>
-  </si>
-  <si>
-    <t>Ban hành theo Thông tư số 107/2017/TT-BTc</t>
   </si>
   <si>
     <r>
@@ -54,25 +48,7 @@
     </r>
   </si>
   <si>
-    <t>ngày 10/10/2017 của Bộ Tài Chính )</t>
-  </si>
-  <si>
-    <t>BẢNG CHẤM CÔNG</t>
-  </si>
-  <si>
     <t>THÁNG 07 NĂM 2026</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>HỌ VÀ TÊN</t>
-  </si>
-  <si>
-    <t>Ngày trong tháng</t>
-  </si>
-  <si>
-    <t>Quy ra công</t>
   </si>
   <si>
     <t xml:space="preserve">1
@@ -259,150 +235,99 @@
     <t>Tổng cộng: 7</t>
   </si>
   <si>
+    <t>Lương Thời gian</t>
+  </si>
+  <si>
+    <t>Hội nghị, học tập</t>
+  </si>
+  <si>
+    <t>Công tác</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>Con ốm</t>
+  </si>
+  <si>
+    <t>Trực</t>
+  </si>
+  <si>
+    <t>Thai sản</t>
+  </si>
+  <si>
+    <t>Trực dịch</t>
+  </si>
+  <si>
+    <t>Nghỉ không lương</t>
+  </si>
+  <si>
+    <t>Nghỉ Phép</t>
+  </si>
+  <si>
+    <t>Bù lễ</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>Trực tiêm chủng</t>
+  </si>
+  <si>
+    <t>TTc</t>
+  </si>
+  <si>
+    <t>Phép chế độ</t>
+  </si>
+  <si>
+    <t>Pcđ</t>
+  </si>
+  <si>
+    <t>Tiêm chủng</t>
+  </si>
+  <si>
+    <t>Tháng 07 Năm 2026</t>
+  </si>
+  <si>
+    <t>Ngày thường</t>
+  </si>
+  <si>
+    <t>Ngày thứ bảy, CN</t>
+  </si>
+  <si>
+    <t>Ngày Lễ</t>
+  </si>
+  <si>
+    <t>Tổng cộng</t>
+  </si>
+  <si>
+    <t>Tổng cộng: 5</t>
+  </si>
+  <si>
     <t>Hải Vân, ngày 31 tháng 07 năm 2026</t>
   </si>
   <si>
-    <t>Bác sĩ Nguyễn Văn Trưởng</t>
-  </si>
-  <si>
-    <t>Ký hiệu chấm công:</t>
-  </si>
-  <si>
-    <t>Lương Thời gian</t>
-  </si>
-  <si>
-    <t>Hội nghị, học tập</t>
-  </si>
-  <si>
-    <t>Nghỉ ốm</t>
-  </si>
-  <si>
-    <t>Ô</t>
-  </si>
-  <si>
-    <t>Công tác</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>Con ốm</t>
-  </si>
-  <si>
-    <t>Cô</t>
-  </si>
-  <si>
-    <t>Trực</t>
-  </si>
-  <si>
-    <t>Thai sản</t>
-  </si>
-  <si>
-    <t>Ts</t>
-  </si>
-  <si>
-    <t>Trực dịch</t>
-  </si>
-  <si>
-    <t>Td</t>
-  </si>
-  <si>
-    <t>Nghỉ không lương</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Chống dịch</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>Nghỉ Phép</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Bù lễ</t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>Trực tiêm chủng</t>
-  </si>
-  <si>
-    <t>TTc</t>
-  </si>
-  <si>
-    <t>Phép chế độ</t>
-  </si>
-  <si>
-    <t>Pcđ</t>
-  </si>
-  <si>
-    <t>Tiêm chủng</t>
+    <t xml:space="preserve">    Người chấm công</t>
+  </si>
+  <si>
+    <t>24h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trực lễ </t>
+  </si>
+  <si>
+    <t>Trực thứ bảy, chủ nhật</t>
+  </si>
+  <si>
+    <t>TD</t>
   </si>
   <si>
     <t>Đơn vị: Trạm Y tế phường Hải Vân</t>
   </si>
   <si>
-    <t>BẢNG CHẤM CÔNG TRỰC</t>
-  </si>
-  <si>
-    <t>Tháng 07 Năm 2026</t>
-  </si>
-  <si>
-    <t>Mã đơn vị QHN:……………….</t>
-  </si>
-  <si>
-    <t>Tổng số ngày trong tháng</t>
-  </si>
-  <si>
-    <t>Ngày thường</t>
-  </si>
-  <si>
-    <t>Ngày thứ bảy, CN</t>
-  </si>
-  <si>
-    <t>Ngày Lễ</t>
-  </si>
-  <si>
-    <t>Tổng cộng</t>
-  </si>
-  <si>
-    <t>Tổng cộng: 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Người chấm công</t>
-  </si>
-  <si>
-    <t>24h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trực lễ </t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Trực thứ bảy, chủ nhật</t>
-  </si>
-  <si>
-    <t>TD</t>
-  </si>
-  <si>
-    <t>BẢNG CHẤM CÔNG HƯỞNG PHỤ CẤP ĐỘC HẠI THEO LƯƠNG</t>
-  </si>
-  <si>
     <t>Tháng 07 năm 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Số ngày công được hưởng </t>
-  </si>
-  <si>
     <t>Tổng cộng:</t>
   </si>
   <si>
@@ -410,12 +335,6 @@
   </si>
   <si>
     <t>Có mặt &lt; 4 giờ :</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>BẢNG CHẤM CÔNG HƯỞNG PHỤ CẤP ĐỘC HẠI BẰNG HIỆN VẬT</t>
   </si>
   <si>
     <t>1 Xuất mức 3</t>
@@ -500,11 +419,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
       <family val="2"/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -559,6 +473,11 @@
       <color theme="1"/>
       <family val="1"/>
       <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -804,9 +723,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -820,7 +736,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -829,68 +745,71 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -979,7 +898,7 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1314,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM30"/>
+  <dimension ref="A1:AM26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.7109375"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -2173,9 +2092,7 @@
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
-      <c r="Y1" s="6" t="s">
-        <v>1</v>
-      </c>
+      <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
       <c r="AA1" s="6"/>
       <c r="AB1" s="6"/>
@@ -2193,7 +2110,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2218,9 +2135,7 @@
       <c r="V2" s="8"/>
       <c r="W2" s="8"/>
       <c r="X2" s="8"/>
-      <c r="Y2" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6"/>
@@ -2238,7 +2153,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2263,9 +2178,7 @@
       <c r="V3" s="8"/>
       <c r="W3" s="8"/>
       <c r="X3" s="8"/>
-      <c r="Y3" s="6" t="s">
-        <v>5</v>
-      </c>
+      <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
       <c r="AA3" s="6"/>
       <c r="AB3" s="6"/>
@@ -2282,9 +2195,7 @@
       <c r="AM3" s="6"/>
     </row>
     <row r="4" ht="20.25" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>6</v>
-      </c>
+      <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2326,7 +2237,7 @@
     </row>
     <row r="5" ht="20.25" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2368,15 +2279,9 @@
       <c r="AM5" s="10"/>
     </row>
     <row r="6" ht="23.25" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
@@ -2407,9 +2312,7 @@
       <c r="AE6" s="14"/>
       <c r="AF6" s="14"/>
       <c r="AG6" s="15"/>
-      <c r="AH6" s="13" t="s">
-        <v>11</v>
-      </c>
+      <c r="AH6" s="13"/>
       <c r="AI6" s="14"/>
       <c r="AJ6" s="14"/>
       <c r="AK6" s="14"/>
@@ -2420,115 +2323,115 @@
       <c r="A7" s="11"/>
       <c r="B7" s="12"/>
       <c r="C7" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="L7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="M7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="N7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="O7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="P7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="Q7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="R7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="S7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="T7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="U7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="V7" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="W7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="16" t="s">
+      <c r="X7" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="16" t="s">
+      <c r="Y7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="R7" s="16" t="s">
+      <c r="Z7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="16" t="s">
+      <c r="AA7" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="T7" s="17" t="s">
+      <c r="AB7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="U7" s="17" t="s">
+      <c r="AC7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="V7" s="16" t="s">
+      <c r="AD7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="W7" s="16" t="s">
+      <c r="AE7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="X7" s="16" t="s">
+      <c r="AF7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="Y7" s="16" t="s">
+      <c r="AG7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="Z7" s="16" t="s">
+      <c r="AH7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="AA7" s="17" t="s">
+      <c r="AI7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="AB7" s="17" t="s">
+      <c r="AJ7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AC7" s="16" t="s">
+      <c r="AK7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AD7" s="16" t="s">
+      <c r="AL7" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="16" t="s">
+      <c r="AM7" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="AF7" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG7" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI7" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ7" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK7" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="AL7" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="AM7" s="20" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -2536,100 +2439,100 @@
         <v>1</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z8" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AA8" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AE8" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AF8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AG8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AH8" s="25">
         <v>23</v>
@@ -2649,100 +2552,100 @@
         <v>2</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N9" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Z9" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AA9" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AB9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AE9" s="23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="AF9" s="23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="AG9" s="23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="AH9" s="25">
         <v>23</v>
@@ -2758,100 +2661,100 @@
         <v>3</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="X10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Z10" s="23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AA10" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AB10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AE10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AG10" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AH10" s="25">
         <v>23</v>
@@ -2867,100 +2770,100 @@
         <v>4</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M11" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="W11" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA11" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AB11" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AC11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AE11" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AF11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AG11" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AH11" s="25">
         <v>23</v>
@@ -2980,100 +2883,100 @@
         <v>5</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U12" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="X12" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Y12" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Z12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA12" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AB12" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AE12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AG12" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AH12" s="25">
         <v>23</v>
@@ -3093,100 +2996,100 @@
         <v>6</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M13" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N13" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P13" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="R13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U13" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V13" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="X13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Y13" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Z13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AA13" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AB13" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AD13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AE13" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF13" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AG13" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AH13" s="25">
         <v>23</v>
@@ -3206,100 +3109,100 @@
         <v>7</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M14" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="R14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S14" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U14" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V14" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="W14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="X14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y14" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AA14" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AB14" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AC14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AD14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AE14" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AF14" s="23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AG14" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AH14" s="25">
         <v>23</v>
@@ -3317,7 +3220,7 @@
     <row r="15" ht="22.5" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
       <c r="B15" s="29" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
@@ -3389,30 +3292,14 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
-      <c r="T16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="U16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="V16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="W16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="X16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>63</v>
-      </c>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="30"/>
       <c r="AB16" s="30"/>
       <c r="AC16" s="30"/>
       <c r="AD16" s="30"/>
@@ -3427,9 +3314,7 @@
       <c r="AM16" s="30"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
-        <v>51</v>
-      </c>
+      <c r="A17" s="31"/>
       <c r="B17" s="31"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -3440,9 +3325,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="31" t="s">
-        <v>51</v>
-      </c>
+      <c r="L17" s="31"/>
       <c r="M17" s="31"/>
       <c r="N17" s="31"/>
       <c r="O17" s="31"/>
@@ -3457,9 +3340,7 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AA17" s="31" t="s">
-        <v>51</v>
-      </c>
+      <c r="AA17" s="31"/>
       <c r="AB17" s="31"/>
       <c r="AC17" s="31"/>
       <c r="AD17" s="31"/>
@@ -3473,415 +3354,375 @@
       <c r="AL17" s="31"/>
       <c r="AM17" s="31"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+    <row r="18" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="31"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="31"/>
+      <c r="AK18" s="31"/>
+      <c r="AL18" s="33"/>
+      <c r="AM18" s="31"/>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="W19" s="38"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="38"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="37"/>
+      <c r="AC19" s="37"/>
+      <c r="AD19" s="38"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
+      <c r="AG19" s="38"/>
+      <c r="AH19" s="39"/>
+      <c r="AI19" s="39"/>
+      <c r="AJ19" s="39"/>
+      <c r="AK19" s="39"/>
+      <c r="AL19" s="39"/>
+      <c r="AM19" s="38"/>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A20" s="40"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="L21" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA21" s="32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="31"/>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
-      <c r="AG22" s="31"/>
-      <c r="AH22" s="31"/>
-      <c r="AI22" s="31"/>
-      <c r="AJ22" s="31"/>
-      <c r="AK22" s="31"/>
-      <c r="AL22" s="34"/>
-      <c r="AM22" s="31"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="38"/>
+      <c r="AE20" s="38"/>
+      <c r="AF20" s="38"/>
+      <c r="AG20" s="38"/>
+      <c r="AH20" s="40"/>
+      <c r="AI20" s="40"/>
+      <c r="AJ20" s="40"/>
+      <c r="AK20" s="40"/>
+      <c r="AL20" s="6"/>
+      <c r="AM20" s="40"/>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A21" s="40"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="W21" s="38"/>
+      <c r="X21" s="38"/>
+      <c r="Y21" s="38"/>
+      <c r="Z21" s="38"/>
+      <c r="AA21" s="38"/>
+      <c r="AB21" s="37"/>
+      <c r="AC21" s="37"/>
+      <c r="AD21" s="38"/>
+      <c r="AE21" s="38"/>
+      <c r="AF21" s="38"/>
+      <c r="AG21" s="38"/>
+      <c r="AH21" s="40"/>
+      <c r="AI21" s="40"/>
+      <c r="AJ21" s="40"/>
+      <c r="AK21" s="40"/>
+      <c r="AL21" s="6"/>
+      <c r="AM21" s="40"/>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A22" s="40"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="W22" s="38"/>
+      <c r="X22" s="38"/>
+      <c r="Y22" s="38"/>
+      <c r="Z22" s="38"/>
+      <c r="AA22" s="38"/>
+      <c r="AB22" s="37"/>
+      <c r="AC22" s="37"/>
+      <c r="AD22" s="38"/>
+      <c r="AE22" s="38"/>
+      <c r="AF22" s="38"/>
+      <c r="AG22" s="38"/>
+      <c r="AH22" s="40"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="40"/>
+      <c r="AK22" s="40"/>
+      <c r="AL22" s="6"/>
+      <c r="AM22" s="40"/>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="L23" s="38"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="39"/>
-      <c r="T23" s="39"/>
-      <c r="U23" s="39"/>
-      <c r="V23" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="W23" s="39"/>
-      <c r="X23" s="39"/>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="39"/>
-      <c r="AA23" s="39"/>
-      <c r="AB23" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC23" s="38"/>
-      <c r="AD23" s="39"/>
-      <c r="AE23" s="39"/>
-      <c r="AF23" s="39"/>
-      <c r="AG23" s="39"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="W23" s="38"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="38"/>
+      <c r="AA23" s="38"/>
+      <c r="AB23" s="37"/>
+      <c r="AC23" s="37"/>
+      <c r="AD23" s="38"/>
+      <c r="AE23" s="38"/>
+      <c r="AF23" s="38"/>
+      <c r="AG23" s="38"/>
       <c r="AH23" s="40"/>
       <c r="AI23" s="40"/>
       <c r="AJ23" s="40"/>
       <c r="AK23" s="40"/>
-      <c r="AL23" s="40"/>
-      <c r="AM23" s="39"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="34"/>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A24" s="41"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="42" t="s">
+      <c r="A24" s="43"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="W24" s="38"/>
+      <c r="X24" s="38"/>
+      <c r="Y24" s="38"/>
+      <c r="Z24" s="38"/>
+      <c r="AA24" s="38"/>
+      <c r="AB24" s="37"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="38"/>
+      <c r="AE24" s="38"/>
+      <c r="AF24" s="38"/>
+      <c r="AG24" s="38"/>
+      <c r="AH24" s="43"/>
+      <c r="AI24" s="43"/>
+      <c r="AJ24" s="43"/>
+      <c r="AK24" s="43"/>
+      <c r="AL24" s="43"/>
+      <c r="AM24" s="43"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A25" s="40"/>
+      <c r="C25" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="38"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="W25" s="38"/>
+      <c r="X25" s="38"/>
+      <c r="Y25" s="38"/>
+      <c r="Z25" s="38"/>
+      <c r="AA25" s="38"/>
+      <c r="AB25" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="38" t="s">
+      <c r="AC25" s="38"/>
+      <c r="AD25" s="40"/>
+      <c r="AE25" s="40"/>
+      <c r="AF25" s="40"/>
+      <c r="AG25" s="40"/>
+      <c r="AL25" s="44"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="C26" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="L24" s="38"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="39" t="s">
+      <c r="K26" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="W24" s="39"/>
-      <c r="X24" s="39"/>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="39"/>
-      <c r="AB24" s="39" t="s">
+      <c r="V26" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="39"/>
-      <c r="AE24" s="39"/>
-      <c r="AF24" s="39"/>
-      <c r="AG24" s="39"/>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="41"/>
-      <c r="AJ24" s="41"/>
-      <c r="AK24" s="41"/>
-      <c r="AL24" s="6"/>
-      <c r="AM24" s="41"/>
-    </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A25" s="41"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="L25" s="38"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="39"/>
-      <c r="T25" s="39"/>
-      <c r="U25" s="39"/>
-      <c r="V25" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="W25" s="39"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="39"/>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="39"/>
-      <c r="AB25" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC25" s="38"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="39"/>
-      <c r="AF25" s="39"/>
-      <c r="AG25" s="39"/>
-      <c r="AH25" s="41"/>
-      <c r="AI25" s="41"/>
-      <c r="AJ25" s="41"/>
-      <c r="AK25" s="41"/>
-      <c r="AL25" s="6"/>
-      <c r="AM25" s="41"/>
-    </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A26" s="41"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="L26" s="38"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="39"/>
-      <c r="S26" s="39"/>
-      <c r="T26" s="39"/>
-      <c r="U26" s="39"/>
-      <c r="V26" s="39" t="s">
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="38"/>
+      <c r="AA26" s="38"/>
+      <c r="AB26" s="38" t="s">
         <v>46</v>
-      </c>
-      <c r="W26" s="39"/>
-      <c r="X26" s="39"/>
-      <c r="Y26" s="39"/>
-      <c r="Z26" s="39"/>
-      <c r="AA26" s="39"/>
-      <c r="AB26" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC26" s="38"/>
-      <c r="AD26" s="39"/>
-      <c r="AE26" s="39"/>
-      <c r="AF26" s="39"/>
-      <c r="AG26" s="39"/>
-      <c r="AH26" s="41"/>
-      <c r="AI26" s="41"/>
-      <c r="AJ26" s="41"/>
-      <c r="AK26" s="41"/>
-      <c r="AL26" s="6"/>
-      <c r="AM26" s="41"/>
-    </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="L27" s="38"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="39"/>
-      <c r="T27" s="39"/>
-      <c r="U27" s="39"/>
-      <c r="V27" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="W27" s="39"/>
-      <c r="X27" s="39"/>
-      <c r="Y27" s="39"/>
-      <c r="Z27" s="39"/>
-      <c r="AA27" s="39"/>
-      <c r="AB27" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC27" s="38"/>
-      <c r="AD27" s="39"/>
-      <c r="AE27" s="39"/>
-      <c r="AF27" s="39"/>
-      <c r="AG27" s="39"/>
-      <c r="AH27" s="41"/>
-      <c r="AI27" s="41"/>
-      <c r="AJ27" s="41"/>
-      <c r="AK27" s="41"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="35"/>
-    </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="38"/>
-      <c r="V28" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="W28" s="39"/>
-      <c r="X28" s="39"/>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="39"/>
-      <c r="AA28" s="39"/>
-      <c r="AB28" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC28" s="38"/>
-      <c r="AD28" s="39"/>
-      <c r="AE28" s="39"/>
-      <c r="AF28" s="39"/>
-      <c r="AG28" s="39"/>
-      <c r="AH28" s="44"/>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="44"/>
-      <c r="AK28" s="44"/>
-      <c r="AL28" s="44"/>
-      <c r="AM28" s="44"/>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A29" s="41"/>
-      <c r="C29" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="39"/>
-      <c r="T29" s="39"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="W29" s="39"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="39"/>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="39"/>
-      <c r="AB29" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="41"/>
-      <c r="AE29" s="41"/>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="41"/>
-      <c r="AL29" s="45"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C30" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="K30" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="V30" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="W30" s="39"/>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="39"/>
-      <c r="AB30" s="39" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3899,20 +3740,20 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="L17:V17"/>
     <mergeCell ref="AA17:AM17"/>
-    <mergeCell ref="C22:K22"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="AB19:AC19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="AB21:AC21"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="AB22:AC22"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C24:G24"/>
     <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="AB25:AC25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="AB26:AC26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="AB27:AC27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="AB28:AC28"/>
+    <mergeCell ref="AB24:AC24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -3921,198 +3762,186 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
-    <col min="1" max="1" width="4" style="46" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" style="46" customWidth="1"/>
-    <col min="3" max="33" width="3.140625" style="46" customWidth="1"/>
-    <col min="34" max="34" width="7" style="47" customWidth="1"/>
-    <col min="35" max="36" width="6" style="47" customWidth="1"/>
-    <col min="37" max="37" width="6.140625" style="47" customWidth="1"/>
-    <col min="38" max="38" width="12.140625" style="46" customWidth="1"/>
-    <col min="39" max="39" width="0.28515625" style="46" customWidth="1"/>
-    <col min="40" max="40" width="9.140625" style="46" customWidth="1"/>
-    <col min="41" max="41" width="7.140625" style="46" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="46" customWidth="1"/>
+    <col min="1" max="1" width="4" style="45" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" style="45" customWidth="1"/>
+    <col min="3" max="33" width="3.140625" style="45" customWidth="1"/>
+    <col min="34" max="34" width="7" style="46" customWidth="1"/>
+    <col min="35" max="36" width="6" style="46" customWidth="1"/>
+    <col min="37" max="37" width="6.140625" style="46" customWidth="1"/>
+    <col min="38" max="38" width="12.140625" style="45" customWidth="1"/>
+    <col min="39" max="39" width="0.28515625" style="45" customWidth="1"/>
+    <col min="40" max="40" width="9.140625" style="45" customWidth="1"/>
+    <col min="41" max="41" width="7.140625" style="45" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
+      <c r="A1" s="47"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="48"/>
+      <c r="AG1" s="48"/>
+      <c r="AH1" s="48"/>
+      <c r="AI1" s="48"/>
+      <c r="AJ1" s="48"/>
+      <c r="AK1" s="48"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-    </row>
-    <row r="3" ht="19.5" customHeight="1" spans="1:37" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="52"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="52"/>
-      <c r="AF3" s="52"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="54"/>
-      <c r="AI3" s="54"/>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-    </row>
-    <row r="4" ht="19.5" customHeight="1" spans="1:37" s="52" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="52"/>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="54"/>
-      <c r="AI4" s="54"/>
-      <c r="AJ4" s="54"/>
-      <c r="AK4" s="54"/>
-    </row>
-    <row r="5" ht="23.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="A2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1" spans="1:37" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="51"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="51"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1" spans="1:37" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="51"/>
+      <c r="AD4" s="51"/>
+      <c r="AE4" s="51"/>
+      <c r="AF4" s="51"/>
+      <c r="AG4" s="51"/>
+      <c r="AH4" s="53"/>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="53"/>
+    </row>
+    <row r="5" ht="23.25" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -4143,221 +3972,225 @@
       <c r="AE5" s="14"/>
       <c r="AF5" s="14"/>
       <c r="AG5" s="15"/>
-      <c r="AH5" s="13" t="s">
-        <v>96</v>
-      </c>
+      <c r="AH5" s="13"/>
       <c r="AI5" s="14"/>
       <c r="AJ5" s="14"/>
       <c r="AK5" s="15"/>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL5" s="45"/>
+      <c r="AM5" s="45"/>
+      <c r="AN5" s="45"/>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="12"/>
       <c r="C6" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="L6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="M6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="N6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="O6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="P6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="Q6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="R6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="S6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="T6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="U6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="V6" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="W6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="X6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="Y6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="Z6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="S6" s="16" t="s">
+      <c r="AA6" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="T6" s="17" t="s">
+      <c r="AB6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="U6" s="17" t="s">
+      <c r="AC6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="AD6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="W6" s="16" t="s">
+      <c r="AE6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="AF6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="Y6" s="16" t="s">
+      <c r="AG6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="Z6" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB6" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD6" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE6" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF6" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG6" s="16" t="s">
-        <v>42</v>
-      </c>
       <c r="AH6" s="18" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="AI6" s="18" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AJ6" s="19" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK6" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="AL6" s="45"/>
+      <c r="AM6" s="45"/>
+      <c r="AN6" s="45"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>1</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="W7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Y7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AB7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AD7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AE7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AF7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AG7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AH7" s="25">
         <v>4</v>
@@ -4369,106 +4202,109 @@
       <c r="AK7" s="26">
         <f>SUM(AH7:AJ7)</f>
       </c>
-    </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL7" s="45"/>
+      <c r="AM7" s="45"/>
+      <c r="AN7" s="45"/>
+    </row>
+    <row r="8" ht="20.25" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>2</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Y8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA8" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AE8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AF8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AG8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AH8" s="25">
         <v>9</v>
@@ -4480,106 +4316,109 @@
       <c r="AK8" s="26">
         <f>SUM(AH8:AJ8)</f>
       </c>
-    </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL8" s="45"/>
+      <c r="AM8" s="45"/>
+      <c r="AN8" s="45"/>
+    </row>
+    <row r="9" ht="20.25" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>3</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="W9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="X9" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Y9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Z9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AB9" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AE9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AF9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AG9" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AH9" s="25">
         <v>1</v>
@@ -4589,106 +4428,109 @@
       <c r="AK9" s="26">
         <f>SUM(AH9:AJ9)</f>
       </c>
-    </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL9" s="45"/>
+      <c r="AM9" s="45"/>
+      <c r="AN9" s="45"/>
+    </row>
+    <row r="10" ht="20.25" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>4</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="W10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="X10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Y10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Z10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AA10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AB10" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AD10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AE10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AF10" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AG10" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AH10" s="25">
         <v>8</v>
@@ -4700,106 +4542,109 @@
       <c r="AK10" s="26">
         <f>SUM(AH10:AJ10)</f>
       </c>
-    </row>
-    <row r="11" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL10" s="45"/>
+      <c r="AM10" s="45"/>
+      <c r="AN10" s="45"/>
+    </row>
+    <row r="11" ht="20.25" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>5</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M11" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="W11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="X11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Y11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA11" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AB11" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AC11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AE11" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AF11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AG11" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AH11" s="25">
         <v>7</v>
@@ -4811,11 +4656,14 @@
       <c r="AK11" s="26">
         <f>SUM(AH11:AJ11)</f>
       </c>
-    </row>
-    <row r="12" ht="20.25" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL11" s="45"/>
+      <c r="AM11" s="45"/>
+      <c r="AN11" s="45"/>
+    </row>
+    <row r="12" ht="20.25" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
@@ -4860,167 +4708,167 @@
       <c r="AK12" s="28">
         <f>SUM(AK7:AK11)</f>
       </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="U13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="V13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="W13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="X13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB13" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC13" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="59"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="59"/>
-      <c r="AH13" s="59"/>
-      <c r="AI13" s="59"/>
-      <c r="AJ13" s="59"/>
-      <c r="AK13" s="59"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A14" s="60"/>
-      <c r="B14" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="51"/>
-      <c r="T14" s="51"/>
-      <c r="U14" s="51"/>
-      <c r="V14" s="51"/>
-      <c r="W14" s="61"/>
-      <c r="X14" s="61"/>
-      <c r="Y14" s="61"/>
-      <c r="Z14" s="61"/>
-      <c r="AA14" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB14" s="62"/>
-      <c r="AC14" s="62"/>
-      <c r="AD14" s="62"/>
-      <c r="AE14" s="62"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-    </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B18" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="L18" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA18" s="32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="61"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="61"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="61"/>
-      <c r="T19" s="61"/>
-      <c r="U19" s="61"/>
-      <c r="V19" s="61"/>
-      <c r="W19" s="61"/>
-      <c r="X19" s="61"/>
-      <c r="Y19" s="61"/>
-      <c r="Z19" s="61"/>
-      <c r="AA19" s="51"/>
-      <c r="AB19" s="51"/>
-      <c r="AC19" s="51"/>
-      <c r="AD19" s="51"/>
-      <c r="AE19" s="51"/>
-      <c r="AF19" s="51"/>
-      <c r="AG19" s="51"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A13" s="55"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="U13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="V13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="W13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB13" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC13" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD13" s="58"/>
+      <c r="AE13" s="58"/>
+      <c r="AF13" s="58"/>
+      <c r="AG13" s="58"/>
+      <c r="AH13" s="58"/>
+      <c r="AI13" s="58"/>
+      <c r="AJ13" s="58"/>
+      <c r="AK13" s="58"/>
+      <c r="AL13" s="45"/>
+      <c r="AM13" s="45"/>
+      <c r="AN13" s="45"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A14" s="59"/>
+      <c r="B14" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="60"/>
+      <c r="Z14" s="60"/>
+      <c r="AA14" s="61"/>
+      <c r="AB14" s="61"/>
+      <c r="AC14" s="61"/>
+      <c r="AD14" s="61"/>
+      <c r="AE14" s="61"/>
+      <c r="AF14" s="61"/>
+      <c r="AG14" s="61"/>
+      <c r="AH14" s="61"/>
+      <c r="AI14" s="61"/>
+      <c r="AJ14" s="61"/>
+      <c r="AK14" s="61"/>
+      <c r="AL14" s="45"/>
+      <c r="AM14" s="45"/>
+      <c r="AN14" s="45"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="62" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A19" s="60"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="50"/>
+      <c r="AB19" s="50"/>
+      <c r="AC19" s="50"/>
+      <c r="AD19" s="50"/>
+      <c r="AE19" s="50"/>
+      <c r="AF19" s="50"/>
+      <c r="AG19" s="50"/>
       <c r="AH19" s="63"/>
       <c r="AI19" s="63"/>
       <c r="AJ19" s="63"/>
       <c r="AK19" s="63"/>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="64" t="s">
-        <v>65</v>
-      </c>
+      <c r="AL19" s="45"/>
+      <c r="AM19" s="45"/>
+      <c r="AN19" s="45"/>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A20" s="60"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="64"/>
       <c r="E20" s="64"/>
       <c r="F20" s="64"/>
@@ -5029,180 +4877,217 @@
       <c r="I20" s="64"/>
       <c r="J20" s="64"/>
       <c r="K20" s="64"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="61"/>
-      <c r="S20" s="61"/>
-      <c r="T20" s="61"/>
-      <c r="U20" s="61"/>
-      <c r="V20" s="61"/>
-      <c r="W20" s="61"/>
-      <c r="X20" s="61"/>
-      <c r="Y20" s="46"/>
-      <c r="Z20" s="61"/>
-      <c r="AA20" s="51"/>
-      <c r="AB20" s="51"/>
-      <c r="AC20" s="51"/>
-      <c r="AD20" s="51"/>
-      <c r="AE20" s="51"/>
-      <c r="AF20" s="51"/>
-      <c r="AG20" s="51"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="60"/>
+      <c r="Y20" s="45"/>
+      <c r="Z20" s="60"/>
+      <c r="AA20" s="50"/>
+      <c r="AB20" s="50"/>
+      <c r="AC20" s="50"/>
+      <c r="AD20" s="50"/>
+      <c r="AE20" s="50"/>
+      <c r="AF20" s="50"/>
+      <c r="AG20" s="50"/>
       <c r="AH20" s="63"/>
       <c r="AI20" s="63"/>
       <c r="AJ20" s="63"/>
       <c r="AK20" s="63"/>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="64" t="s">
-        <v>52</v>
-      </c>
+      <c r="AL20" s="45"/>
+      <c r="AM20" s="45"/>
+      <c r="AN20" s="45"/>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="64"/>
       <c r="L21" s="64"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="46"/>
-      <c r="Z21" s="46"/>
-      <c r="AA21" s="46"/>
-      <c r="AB21" s="46"/>
-      <c r="AC21" s="46"/>
-      <c r="AD21" s="46"/>
-      <c r="AE21" s="46"/>
-      <c r="AF21" s="46"/>
-      <c r="AG21" s="46"/>
-      <c r="AH21" s="47"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
+      <c r="U21" s="45"/>
+      <c r="V21" s="45"/>
+      <c r="W21" s="45"/>
+      <c r="X21" s="45"/>
+      <c r="Y21" s="45"/>
+      <c r="Z21" s="45"/>
+      <c r="AA21" s="45"/>
+      <c r="AB21" s="45"/>
+      <c r="AC21" s="45"/>
+      <c r="AD21" s="45"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="46"/>
       <c r="AI21" s="65"/>
       <c r="AJ21" s="66"/>
       <c r="AK21" s="66"/>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A22" s="46"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="64" t="s">
-        <v>105</v>
-      </c>
+      <c r="AL21" s="45"/>
+      <c r="AM21" s="45"/>
+      <c r="AN21" s="45"/>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="64"/>
       <c r="L22" s="64"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
-      <c r="O22" s="46"/>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="46"/>
-      <c r="U22" s="46"/>
-      <c r="V22" s="46"/>
-      <c r="W22" s="46"/>
-      <c r="X22" s="46"/>
-      <c r="Y22" s="46"/>
-      <c r="Z22" s="46"/>
-      <c r="AA22" s="46"/>
-      <c r="AB22" s="46"/>
-      <c r="AC22" s="46"/>
-      <c r="AD22" s="46"/>
-      <c r="AE22" s="46"/>
-      <c r="AF22" s="46"/>
-      <c r="AG22" s="46"/>
-      <c r="AH22" s="47"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="45"/>
+      <c r="S22" s="45"/>
+      <c r="T22" s="45"/>
+      <c r="U22" s="45"/>
+      <c r="V22" s="45"/>
+      <c r="W22" s="45"/>
+      <c r="X22" s="45"/>
+      <c r="Y22" s="45"/>
+      <c r="Z22" s="45"/>
+      <c r="AA22" s="45"/>
+      <c r="AB22" s="45"/>
+      <c r="AC22" s="45"/>
+      <c r="AD22" s="45"/>
+      <c r="AE22" s="45"/>
+      <c r="AF22" s="45"/>
+      <c r="AG22" s="45"/>
+      <c r="AH22" s="46"/>
       <c r="AI22" s="65"/>
-      <c r="AJ22" s="47"/>
-      <c r="AK22" s="47"/>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AJ22" s="46"/>
+      <c r="AK22" s="46"/>
+      <c r="AL22" s="45"/>
+      <c r="AM22" s="45"/>
+      <c r="AN22" s="45"/>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="67"/>
       <c r="B23" s="67"/>
-      <c r="C23" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="L23" s="46"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="51"/>
-      <c r="S23" s="51"/>
-      <c r="T23" s="51"/>
-      <c r="U23" s="51"/>
-      <c r="V23" s="46"/>
-      <c r="W23" s="46"/>
-      <c r="X23" s="46"/>
-      <c r="Y23" s="46"/>
-      <c r="Z23" s="46"/>
-      <c r="AA23" s="46"/>
-      <c r="AB23" s="46"/>
-      <c r="AC23" s="46"/>
-      <c r="AD23" s="46"/>
-      <c r="AE23" s="46"/>
-      <c r="AF23" s="46"/>
-      <c r="AG23" s="46"/>
-      <c r="AH23" s="47"/>
+      <c r="C23" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" s="45"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="50"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="45"/>
+      <c r="W23" s="45"/>
+      <c r="X23" s="45"/>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="45"/>
+      <c r="AA23" s="45"/>
+      <c r="AB23" s="45"/>
+      <c r="AC23" s="45"/>
+      <c r="AD23" s="45"/>
+      <c r="AE23" s="45"/>
+      <c r="AF23" s="45"/>
+      <c r="AG23" s="45"/>
+      <c r="AH23" s="46"/>
       <c r="AI23" s="65"/>
-      <c r="AJ23" s="47"/>
-      <c r="AK23" s="47"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="46"/>
+      <c r="AJ23" s="46"/>
+      <c r="AK23" s="46"/>
+      <c r="AL23" s="45"/>
+      <c r="AM23" s="45"/>
+      <c r="AN23" s="45"/>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A24" s="45"/>
       <c r="B24" s="68"/>
       <c r="C24" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="46"/>
+        <v>62</v>
+      </c>
+      <c r="D24" s="45"/>
       <c r="E24" s="64"/>
       <c r="F24" s="64"/>
       <c r="G24" s="64"/>
       <c r="H24" s="64"/>
       <c r="I24" s="64"/>
-      <c r="J24" s="46"/>
+      <c r="J24" s="45"/>
       <c r="K24" s="64" t="s">
-        <v>107</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="45"/>
+      <c r="U24" s="45"/>
+      <c r="V24" s="45"/>
+      <c r="W24" s="45"/>
+      <c r="X24" s="45"/>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="45"/>
+      <c r="AA24" s="45"/>
+      <c r="AB24" s="45"/>
+      <c r="AC24" s="45"/>
+      <c r="AD24" s="45"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="46"/>
+      <c r="AI24" s="46"/>
+      <c r="AJ24" s="46"/>
+      <c r="AK24" s="46"/>
+      <c r="AL24" s="45"/>
+      <c r="AM24" s="45"/>
+      <c r="AN24" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -5230,7 +5115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.5703125" customWidth="1"/>
@@ -5240,16 +5125,14 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="69"/>
       <c r="F1" s="70"/>
-      <c r="G1" s="71" t="s">
-        <v>108</v>
-      </c>
+      <c r="G1" s="71"/>
       <c r="H1" s="71"/>
       <c r="I1" s="71"/>
       <c r="J1" s="71"/>
@@ -5280,14 +5163,14 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="E2" s="72"/>
       <c r="F2" s="72"/>
       <c r="G2" s="73" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="H2" s="73"/>
       <c r="I2" s="73"/>
@@ -5318,9 +5201,7 @@
       <c r="AH2" s="73"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
-        <v>4</v>
-      </c>
+      <c r="A3" s="74"/>
       <c r="B3" s="74"/>
       <c r="C3" s="74"/>
       <c r="D3" s="3"/>
@@ -5358,7 +5239,7 @@
     <row r="4" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="74"/>
       <c r="B4" s="74"/>
-      <c r="C4" s="48"/>
+      <c r="C4" s="47"/>
       <c r="D4" s="3"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -5392,15 +5273,9 @@
       <c r="AH4" s="6"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>10</v>
-      </c>
+      <c r="A5" s="75"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
       <c r="D5" s="77"/>
       <c r="E5" s="77"/>
       <c r="F5" s="77"/>
@@ -5431,105 +5306,103 @@
       <c r="AE5" s="77"/>
       <c r="AF5" s="77"/>
       <c r="AG5" s="78"/>
-      <c r="AH5" s="79" t="s">
-        <v>110</v>
-      </c>
+      <c r="AH5" s="79"/>
     </row>
     <row r="6" ht="29.25" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="75"/>
       <c r="B6" s="75"/>
       <c r="C6" s="80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="80" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="81" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="81" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="80" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="L6" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="M6" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="N6" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="81" t="s">
+      <c r="O6" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="80" t="s">
+      <c r="P6" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="80" t="s">
+      <c r="Q6" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="80" t="s">
+      <c r="R6" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="80" t="s">
+      <c r="S6" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="80" t="s">
+      <c r="T6" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="81" t="s">
+      <c r="U6" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="81" t="s">
+      <c r="V6" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="O6" s="80" t="s">
+      <c r="W6" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="P6" s="80" t="s">
+      <c r="X6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="80" t="s">
+      <c r="Y6" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="R6" s="80" t="s">
+      <c r="Z6" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="S6" s="80" t="s">
+      <c r="AA6" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="T6" s="81" t="s">
+      <c r="AB6" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="U6" s="81" t="s">
+      <c r="AC6" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="V6" s="80" t="s">
+      <c r="AD6" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="W6" s="80" t="s">
+      <c r="AE6" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="X6" s="80" t="s">
+      <c r="AF6" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="Y6" s="80" t="s">
+      <c r="AG6" s="80" t="s">
         <v>34</v>
-      </c>
-      <c r="Z6" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA6" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB6" s="81" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC6" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD6" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE6" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF6" s="80" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG6" s="80" t="s">
-        <v>42</v>
       </c>
       <c r="AH6" s="82"/>
     </row>
@@ -5538,100 +5411,100 @@
         <v>1</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M7" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N7" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="U7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="X7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA7" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="AB7" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD7" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AE7" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AF7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AG7" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AH7" s="83">
         <v>23</v>
@@ -5640,7 +5513,7 @@
     <row r="8" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C8" s="85"/>
       <c r="D8" s="85"/>
@@ -5677,7 +5550,7 @@
         <f>SUM(AH7:AH7)</f>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:35" s="86" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:40" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="87"/>
       <c r="B9" s="87"/>
       <c r="C9" s="87"/>
@@ -5698,22 +5571,22 @@
       <c r="R9" s="88"/>
       <c r="S9" s="88"/>
       <c r="T9" s="88" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U9" s="88" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V9" s="86" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="W9" s="89" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="X9" s="89" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Y9" s="90" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="Z9" s="90"/>
       <c r="AA9" s="90"/>
@@ -5725,13 +5598,18 @@
       <c r="AG9" s="90"/>
       <c r="AH9" s="90"/>
       <c r="AI9" s="86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="AJ9" s="86"/>
+      <c r="AK9" s="86"/>
+      <c r="AL9" s="86"/>
+      <c r="AM9" s="86"/>
+      <c r="AN9" s="86"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:40" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="91"/>
       <c r="B10" s="92" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C10" s="91"/>
       <c r="D10" s="93"/>
@@ -5742,9 +5620,7 @@
       <c r="I10" s="93"/>
       <c r="J10" s="93"/>
       <c r="K10" s="93"/>
-      <c r="L10" s="94" t="s">
-        <v>51</v>
-      </c>
+      <c r="L10" s="94"/>
       <c r="M10" s="94"/>
       <c r="N10" s="94"/>
       <c r="O10" s="94"/>
@@ -5757,9 +5633,7 @@
       <c r="V10" s="94"/>
       <c r="W10" s="86"/>
       <c r="X10" s="91"/>
-      <c r="Y10" s="95" t="s">
-        <v>51</v>
-      </c>
+      <c r="Y10" s="95"/>
       <c r="Z10" s="95"/>
       <c r="AA10" s="95"/>
       <c r="AB10" s="95"/>
@@ -5769,24 +5643,24 @@
       <c r="AF10" s="95"/>
       <c r="AG10" s="95"/>
       <c r="AH10" s="95"/>
+      <c r="AI10" s="86"/>
+      <c r="AJ10" s="86"/>
+      <c r="AK10" s="86"/>
+      <c r="AL10" s="86"/>
+      <c r="AM10" s="86"/>
+      <c r="AN10" s="86"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B14" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y14" s="32" t="s">
-        <v>64</v>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="62" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="48"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="1"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5823,9 +5697,7 @@
     <row r="16" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="97"/>
-      <c r="C16" s="98" t="s">
-        <v>65</v>
-      </c>
+      <c r="C16" s="98"/>
       <c r="D16" s="98"/>
       <c r="E16" s="98"/>
       <c r="F16" s="98"/>
@@ -5861,8 +5733,8 @@
     <row r="17" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="99"/>
-      <c r="C17" s="41" t="s">
-        <v>112</v>
+      <c r="C17" s="40" t="s">
+        <v>87</v>
       </c>
       <c r="D17" s="100"/>
       <c r="E17" s="100"/>
@@ -5871,9 +5743,7 @@
       <c r="H17" s="100"/>
       <c r="I17" s="102"/>
       <c r="J17" s="102"/>
-      <c r="K17" s="103" t="s">
-        <v>50</v>
-      </c>
+      <c r="K17" s="103"/>
       <c r="L17" s="103"/>
       <c r="M17" s="100"/>
       <c r="N17" s="100"/>
@@ -5899,10 +5769,10 @@
       <c r="AH17" s="31"/>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A18" s="41"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="69"/>
-      <c r="C18" s="41" t="s">
-        <v>113</v>
+      <c r="C18" s="40" t="s">
+        <v>88</v>
       </c>
       <c r="D18" s="100"/>
       <c r="E18" s="100"/>
@@ -5911,9 +5781,7 @@
       <c r="H18" s="104"/>
       <c r="I18" s="102"/>
       <c r="J18" s="102"/>
-      <c r="K18" s="103" t="s">
-        <v>114</v>
-      </c>
+      <c r="K18" s="103"/>
       <c r="L18" s="103"/>
       <c r="M18" s="100"/>
       <c r="N18" s="100"/>
@@ -5939,10 +5807,10 @@
       <c r="AH18" s="6"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="41"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="69"/>
-      <c r="C19" s="41" t="s">
-        <v>74</v>
+      <c r="C19" s="40" t="s">
+        <v>60</v>
       </c>
       <c r="D19" s="100"/>
       <c r="E19" s="100"/>
@@ -5951,9 +5819,7 @@
       <c r="H19" s="100"/>
       <c r="I19" s="102"/>
       <c r="J19" s="102"/>
-      <c r="K19" s="103" t="s">
-        <v>52</v>
-      </c>
+      <c r="K19" s="103"/>
       <c r="L19" s="103"/>
       <c r="M19" s="100"/>
       <c r="N19" s="100"/>
@@ -6005,7 +5871,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.85546875" customWidth="1"/>
@@ -6014,17 +5880,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="71" t="s">
-        <v>115</v>
-      </c>
+      <c r="A1" s="47"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="71"/>
       <c r="H1" s="71"/>
       <c r="I1" s="71"/>
       <c r="J1" s="71"/>
@@ -6054,16 +5916,16 @@
       <c r="AH1" s="71"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="A2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="73" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="H2" s="73"/>
       <c r="I2" s="73"/>
@@ -6094,14 +5956,12 @@
       <c r="AH2" s="73"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -6134,7 +5994,7 @@
     <row r="4" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="74"/>
       <c r="B4" s="74"/>
-      <c r="C4" s="48"/>
+      <c r="C4" s="47"/>
       <c r="D4" s="3"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -6168,15 +6028,9 @@
       <c r="AH4" s="6"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="105" t="s">
-        <v>10</v>
-      </c>
+      <c r="A5" s="75"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="105"/>
       <c r="D5" s="106"/>
       <c r="E5" s="106"/>
       <c r="F5" s="106"/>
@@ -6207,9 +6061,7 @@
       <c r="AE5" s="106"/>
       <c r="AF5" s="106"/>
       <c r="AG5" s="107"/>
-      <c r="AH5" s="79" t="s">
-        <v>110</v>
-      </c>
+      <c r="AH5" s="79"/>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="75"/>
@@ -6312,100 +6164,100 @@
     <row r="7" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="75"/>
       <c r="B7" s="108" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="C7" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="L7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="M7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="N7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="O7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="P7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="Q7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="R7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="S7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="T7" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="U7" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="24" t="s">
+      <c r="V7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="O7" s="23" t="s">
+      <c r="W7" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="23" t="s">
+      <c r="X7" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="23" t="s">
+      <c r="Y7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="R7" s="23" t="s">
+      <c r="Z7" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="23" t="s">
+      <c r="AA7" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="T7" s="24" t="s">
+      <c r="AB7" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="U7" s="24" t="s">
+      <c r="AC7" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="V7" s="23" t="s">
+      <c r="AD7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="W7" s="23" t="s">
+      <c r="AE7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="X7" s="23" t="s">
+      <c r="AF7" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="Y7" s="23" t="s">
+      <c r="AG7" s="23" t="s">
         <v>34</v>
-      </c>
-      <c r="Z7" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA7" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB7" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC7" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD7" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE7" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG7" s="23" t="s">
-        <v>42</v>
       </c>
       <c r="AH7" s="82"/>
     </row>
@@ -6414,100 +6266,100 @@
         <v>1</v>
       </c>
       <c r="B8" s="109" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="X8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Z8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AC8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AE8" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AF8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AG8" s="23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AH8" s="83">
         <v>25</v>
@@ -6516,7 +6368,7 @@
     <row r="9" ht="22.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" s="84"/>
       <c r="B9" s="85" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -6553,7 +6405,7 @@
         <f>SUM(AH8:AH8)</f>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:35" s="86" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" spans="1:40" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="87"/>
       <c r="B10" s="87"/>
       <c r="C10" s="87"/>
@@ -6574,22 +6426,22 @@
       <c r="R10" s="88"/>
       <c r="S10" s="88"/>
       <c r="T10" s="88" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="U10" s="88" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="V10" s="86" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="W10" s="89" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="X10" s="89" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Y10" s="90" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="Z10" s="90"/>
       <c r="AA10" s="90"/>
@@ -6601,13 +6453,18 @@
       <c r="AG10" s="90"/>
       <c r="AH10" s="90"/>
       <c r="AI10" s="86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:34" s="86" customFormat="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="AJ10" s="86"/>
+      <c r="AK10" s="86"/>
+      <c r="AL10" s="86"/>
+      <c r="AM10" s="86"/>
+      <c r="AN10" s="86"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:40" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="91"/>
       <c r="B11" s="92" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C11" s="91"/>
       <c r="D11" s="93"/>
@@ -6618,9 +6475,7 @@
       <c r="I11" s="93"/>
       <c r="J11" s="93"/>
       <c r="K11" s="93"/>
-      <c r="L11" s="94" t="s">
-        <v>51</v>
-      </c>
+      <c r="L11" s="94"/>
       <c r="M11" s="94"/>
       <c r="N11" s="94"/>
       <c r="O11" s="94"/>
@@ -6633,9 +6488,7 @@
       <c r="V11" s="94"/>
       <c r="W11" s="86"/>
       <c r="X11" s="91"/>
-      <c r="Y11" s="95" t="s">
-        <v>51</v>
-      </c>
+      <c r="Y11" s="95"/>
       <c r="Z11" s="95"/>
       <c r="AA11" s="95"/>
       <c r="AB11" s="95"/>
@@ -6645,24 +6498,24 @@
       <c r="AF11" s="95"/>
       <c r="AG11" s="95"/>
       <c r="AH11" s="95"/>
+      <c r="AI11" s="86"/>
+      <c r="AJ11" s="86"/>
+      <c r="AK11" s="86"/>
+      <c r="AL11" s="86"/>
+      <c r="AM11" s="86"/>
+      <c r="AN11" s="86"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B15" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y15" s="32" t="s">
-        <v>64</v>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="62" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="48"/>
+      <c r="B16" s="47"/>
       <c r="C16" s="1"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6735,7 +6588,7 @@
     <row r="18" ht="15.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="99"/>
-      <c r="C18" s="41"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="100"/>
       <c r="E18" s="100"/>
       <c r="F18" s="101"/>
@@ -6769,9 +6622,9 @@
       <c r="AH18" s="31"/>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="41"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="69"/>
-      <c r="C19" s="41"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="100"/>
       <c r="E19" s="100"/>
       <c r="F19" s="101"/>
@@ -6805,9 +6658,9 @@
       <c r="AH19" s="6"/>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="41"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="69"/>
-      <c r="C20" s="41"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="100"/>
       <c r="E20" s="100"/>
       <c r="F20" s="101"/>

--- a/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
+++ b/Bao_cao_cham_cong_Thang_7_2026_TEST.xlsx
@@ -5530,6 +5530,7 @@
       <c r="S9" s="92"/>
       <c r="T9" s="92"/>
       <c r="U9" s="92"/>
+      <c r="V9" s="90"/>
       <c r="W9" s="93"/>
       <c r="X9" s="93"/>
       <c r="Y9" s="94" t="s">
@@ -6315,6 +6316,7 @@
       <c r="S10" s="92"/>
       <c r="T10" s="92"/>
       <c r="U10" s="92"/>
+      <c r="V10" s="90"/>
       <c r="W10" s="93"/>
       <c r="X10" s="93"/>
       <c r="Y10" s="94" t="s">
